--- a/research/traditional_assets/database/data/mexico/mexico_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_beverage_soft.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09089934325511963</v>
+        <v>0.09065814522535426</v>
       </c>
       <c r="C2">
-        <v>16068.08876138827</v>
+        <v>15981.0873331957</v>
       </c>
       <c r="D2">
-        <v>14635.28876138827</v>
+        <v>14713.9813331957</v>
       </c>
       <c r="E2">
-        <v>-2507.6</v>
+        <v>-2341.906</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>165.694</v>
       </c>
       <c r="G2">
         <v>1432.8</v>
@@ -1585,28 +1585,28 @@
         <v>1831.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.334408199999999</v>
       </c>
       <c r="N2">
-        <v>1831.9</v>
+        <v>1823.5655918</v>
       </c>
       <c r="O2">
-        <v>549.5700000000001</v>
+        <v>547.0696775399999</v>
       </c>
       <c r="P2">
-        <v>1282.33</v>
+        <v>1276.49591426</v>
       </c>
       <c r="Q2">
-        <v>1682.33</v>
+        <v>1676.49591426</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09089934325511963</v>
+        <v>0.09121822750035784</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6608905505572897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>219.7996493620267</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09065814522535426</v>
+        <v>0.0904169471955889</v>
       </c>
       <c r="C3">
-        <v>15981.0873331957</v>
+        <v>15894.93672490319</v>
       </c>
       <c r="D3">
-        <v>14713.9813331957</v>
+        <v>14793.52472490319</v>
       </c>
       <c r="E3">
-        <v>-2341.906</v>
+        <v>-2176.212</v>
       </c>
       <c r="F3">
-        <v>165.694</v>
+        <v>331.388</v>
       </c>
       <c r="G3">
         <v>1432.8</v>
@@ -1667,28 +1667,28 @@
         <v>1831.9</v>
       </c>
       <c r="M3">
-        <v>8.334408199999999</v>
+        <v>16.6688164</v>
       </c>
       <c r="N3">
-        <v>1823.5655918</v>
+        <v>1815.2311836</v>
       </c>
       <c r="O3">
-        <v>547.0696775399999</v>
+        <v>544.56935508</v>
       </c>
       <c r="P3">
-        <v>1276.49591426</v>
+        <v>1270.66182852</v>
       </c>
       <c r="Q3">
-        <v>1676.49591426</v>
+        <v>1670.66182852</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09121822750035784</v>
+        <v>0.09154361958733562</v>
       </c>
       <c r="T3">
-        <v>0.6608905505572897</v>
+        <v>0.6656254019010159</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>219.7996493620267</v>
+        <v>109.8998246810134</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0904169471955889</v>
+        <v>0.09017574916582355</v>
       </c>
       <c r="C4">
-        <v>15894.93672490319</v>
+        <v>15809.65081003992</v>
       </c>
       <c r="D4">
-        <v>14793.52472490319</v>
+        <v>14873.93281003992</v>
       </c>
       <c r="E4">
-        <v>-2176.212</v>
+        <v>-2010.518</v>
       </c>
       <c r="F4">
-        <v>331.388</v>
+        <v>497.0819999999999</v>
       </c>
       <c r="G4">
         <v>1432.8</v>
@@ -1749,28 +1749,28 @@
         <v>1831.9</v>
       </c>
       <c r="M4">
-        <v>16.6688164</v>
+        <v>25.0032246</v>
       </c>
       <c r="N4">
-        <v>1815.2311836</v>
+        <v>1806.8967754</v>
       </c>
       <c r="O4">
-        <v>544.56935508</v>
+        <v>542.06903262</v>
       </c>
       <c r="P4">
-        <v>1270.66182852</v>
+        <v>1264.82774278</v>
       </c>
       <c r="Q4">
-        <v>1670.66182852</v>
+        <v>1664.82774278</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09154361958733562</v>
+        <v>0.09187572078950881</v>
       </c>
       <c r="T4">
-        <v>0.6656254019010159</v>
+        <v>0.6704578790456436</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.8998246810134</v>
+        <v>73.26654978734224</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09017574916582355</v>
+        <v>0.08993455113605819</v>
       </c>
       <c r="C5">
-        <v>15809.65081003992</v>
+        <v>15725.24376541382</v>
       </c>
       <c r="D5">
-        <v>14873.93281003992</v>
+        <v>14955.21976541382</v>
       </c>
       <c r="E5">
-        <v>-2010.518</v>
+        <v>-1844.824</v>
       </c>
       <c r="F5">
-        <v>497.0819999999999</v>
+        <v>662.776</v>
       </c>
       <c r="G5">
         <v>1432.8</v>
@@ -1831,28 +1831,28 @@
         <v>1831.9</v>
       </c>
       <c r="M5">
-        <v>25.0032246</v>
+        <v>33.33763279999999</v>
       </c>
       <c r="N5">
-        <v>1806.8967754</v>
+        <v>1798.5623672</v>
       </c>
       <c r="O5">
-        <v>542.06903262</v>
+        <v>539.56871016</v>
       </c>
       <c r="P5">
-        <v>1264.82774278</v>
+        <v>1258.99365704</v>
       </c>
       <c r="Q5">
-        <v>1664.82774278</v>
+        <v>1658.99365704</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09187572078950881</v>
+        <v>0.09221474076672728</v>
       </c>
       <c r="T5">
-        <v>0.6704578790456436</v>
+        <v>0.6753910327974509</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.26654978734224</v>
+        <v>54.94991234050669</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08993455113605819</v>
+        <v>0.08969335310629283</v>
       </c>
       <c r="C6">
-        <v>15725.24376541382</v>
+        <v>15641.7300794443</v>
       </c>
       <c r="D6">
-        <v>14955.21976541382</v>
+        <v>15037.4000794443</v>
       </c>
       <c r="E6">
-        <v>-1844.824</v>
+        <v>-1679.13</v>
       </c>
       <c r="F6">
-        <v>662.776</v>
+        <v>828.4699999999999</v>
       </c>
       <c r="G6">
         <v>1432.8</v>
@@ -1913,28 +1913,28 @@
         <v>1831.9</v>
       </c>
       <c r="M6">
-        <v>33.33763279999999</v>
+        <v>41.67204099999999</v>
       </c>
       <c r="N6">
-        <v>1798.5623672</v>
+        <v>1790.227959</v>
       </c>
       <c r="O6">
-        <v>539.56871016</v>
+        <v>537.0683877</v>
       </c>
       <c r="P6">
-        <v>1258.99365704</v>
+        <v>1253.1595713</v>
       </c>
       <c r="Q6">
-        <v>1658.99365704</v>
+        <v>1653.1595713</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09221474076672728</v>
+        <v>0.09256089800662404</v>
       </c>
       <c r="T6">
-        <v>0.6753910327974509</v>
+        <v>0.6804280424177175</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.94991234050669</v>
+        <v>43.95992987240535</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08969335310629283</v>
+        <v>0.08945215507652747</v>
       </c>
       <c r="C7">
-        <v>15641.7300794443</v>
+        <v>15559.1245607712</v>
       </c>
       <c r="D7">
-        <v>15037.4000794443</v>
+        <v>15120.48856077121</v>
       </c>
       <c r="E7">
-        <v>-1679.13</v>
+        <v>-1513.436</v>
       </c>
       <c r="F7">
-        <v>828.4699999999999</v>
+        <v>994.164</v>
       </c>
       <c r="G7">
         <v>1432.8</v>
@@ -1995,28 +1995,28 @@
         <v>1831.9</v>
       </c>
       <c r="M7">
-        <v>41.67204099999999</v>
+        <v>50.0064492</v>
       </c>
       <c r="N7">
-        <v>1790.227959</v>
+        <v>1781.8935508</v>
       </c>
       <c r="O7">
-        <v>537.0683877</v>
+        <v>534.56806524</v>
       </c>
       <c r="P7">
-        <v>1253.1595713</v>
+        <v>1247.32548556</v>
       </c>
       <c r="Q7">
-        <v>1653.1595713</v>
+        <v>1647.32548556</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09256089800662404</v>
+        <v>0.09291442029417815</v>
       </c>
       <c r="T7">
-        <v>0.6804280424177175</v>
+        <v>0.6855722224554365</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.95992987240535</v>
+        <v>36.63327489367112</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08945215507652747</v>
+        <v>0.08921095704676212</v>
       </c>
       <c r="C8">
-        <v>15559.1245607712</v>
+        <v>15477.44234715083</v>
       </c>
       <c r="D8">
-        <v>15120.48856077121</v>
+        <v>15204.50034715083</v>
       </c>
       <c r="E8">
-        <v>-1513.436</v>
+        <v>-1347.742</v>
       </c>
       <c r="F8">
-        <v>994.1639999999999</v>
+        <v>1159.858</v>
       </c>
       <c r="G8">
         <v>1432.8</v>
@@ -2077,28 +2077,28 @@
         <v>1831.9</v>
       </c>
       <c r="M8">
-        <v>50.00644919999999</v>
+        <v>58.34085739999998</v>
       </c>
       <c r="N8">
-        <v>1781.8935508</v>
+        <v>1773.5591426</v>
       </c>
       <c r="O8">
-        <v>534.56806524</v>
+        <v>532.06774278</v>
       </c>
       <c r="P8">
-        <v>1247.32548556</v>
+        <v>1241.49139982</v>
       </c>
       <c r="Q8">
-        <v>1647.32548556</v>
+        <v>1641.49139982</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09291442029417815</v>
+        <v>0.09327554521157216</v>
       </c>
       <c r="T8">
-        <v>0.6855722224554365</v>
+        <v>0.6908270300208484</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.63327489367112</v>
+        <v>31.39994990886096</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0892109570467621</v>
+        <v>0.08896975901699676</v>
       </c>
       <c r="C9">
-        <v>15477.44234715083</v>
+        <v>15396.69891465007</v>
       </c>
       <c r="D9">
-        <v>15204.50034715084</v>
+        <v>15289.45091465007</v>
       </c>
       <c r="E9">
-        <v>-1347.742</v>
+        <v>-1182.048</v>
       </c>
       <c r="F9">
-        <v>1159.858</v>
+        <v>1325.552</v>
       </c>
       <c r="G9">
         <v>1432.8</v>
@@ -2159,28 +2159,28 @@
         <v>1831.9</v>
       </c>
       <c r="M9">
-        <v>58.3408574</v>
+        <v>66.67526559999999</v>
       </c>
       <c r="N9">
-        <v>1773.5591426</v>
+        <v>1765.2247344</v>
       </c>
       <c r="O9">
-        <v>532.06774278</v>
+        <v>529.56742032</v>
       </c>
       <c r="P9">
-        <v>1241.49139982</v>
+        <v>1235.65731408</v>
       </c>
       <c r="Q9">
-        <v>1641.49139982</v>
+        <v>1635.65731408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09327554521157216</v>
+        <v>0.09364452067064866</v>
       </c>
       <c r="T9">
-        <v>0.6908270300208484</v>
+        <v>0.6961960725333345</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.39994990886096</v>
+        <v>27.47495617025334</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08896975901699676</v>
+        <v>0.08872856098723139</v>
       </c>
       <c r="C10">
-        <v>15396.69891465007</v>
+        <v>15316.91008715061</v>
       </c>
       <c r="D10">
-        <v>15289.45091465007</v>
+        <v>15375.35608715061</v>
       </c>
       <c r="E10">
-        <v>-1182.048</v>
+        <v>-1016.354</v>
       </c>
       <c r="F10">
-        <v>1325.552</v>
+        <v>1491.246</v>
       </c>
       <c r="G10">
         <v>1432.8</v>
@@ -2241,28 +2241,28 @@
         <v>1831.9</v>
       </c>
       <c r="M10">
-        <v>66.67526559999999</v>
+        <v>75.00967379999997</v>
       </c>
       <c r="N10">
-        <v>1765.2247344</v>
+        <v>1756.8903262</v>
       </c>
       <c r="O10">
-        <v>529.56742032</v>
+        <v>527.06709786</v>
       </c>
       <c r="P10">
-        <v>1235.65731408</v>
+        <v>1229.82322834</v>
       </c>
       <c r="Q10">
-        <v>1635.65731408</v>
+        <v>1629.82322834</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09364452067064866</v>
+        <v>0.09402160548047406</v>
       </c>
       <c r="T10">
-        <v>0.6961960725333345</v>
+        <v>0.7016831159801609</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.47495617025334</v>
+        <v>24.42218326244742</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08872856098723139</v>
+        <v>0.08848736295746604</v>
       </c>
       <c r="C11">
-        <v>15316.91008715061</v>
+        <v>15238.09204617522</v>
       </c>
       <c r="D11">
-        <v>15375.35608715061</v>
+        <v>15462.23204617522</v>
       </c>
       <c r="E11">
-        <v>-1016.354</v>
+        <v>-850.6600000000003</v>
       </c>
       <c r="F11">
-        <v>1491.246</v>
+        <v>1656.94</v>
       </c>
       <c r="G11">
         <v>1432.8</v>
@@ -2323,28 +2323,28 @@
         <v>1831.9</v>
       </c>
       <c r="M11">
-        <v>75.00967379999997</v>
+        <v>83.34408199999997</v>
       </c>
       <c r="N11">
-        <v>1756.8903262</v>
+        <v>1748.555918</v>
       </c>
       <c r="O11">
-        <v>527.06709786</v>
+        <v>524.5667754</v>
       </c>
       <c r="P11">
-        <v>1229.82322834</v>
+        <v>1223.9891426</v>
       </c>
       <c r="Q11">
-        <v>1629.82322834</v>
+        <v>1623.9891426</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09402160548047406</v>
+        <v>0.09440706995274004</v>
       </c>
       <c r="T11">
-        <v>0.7016831159801609</v>
+        <v>0.7072920937258056</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.42218326244742</v>
+        <v>21.97996493620268</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08848736295746604</v>
+        <v>0.08824616492770068</v>
       </c>
       <c r="C12">
-        <v>15238.09204617522</v>
+        <v>15160.2613410492</v>
       </c>
       <c r="D12">
-        <v>15462.23204617522</v>
+        <v>15550.0953410492</v>
       </c>
       <c r="E12">
-        <v>-850.6600000000001</v>
+        <v>-684.9660000000001</v>
       </c>
       <c r="F12">
-        <v>1656.94</v>
+        <v>1822.634</v>
       </c>
       <c r="G12">
         <v>1432.8</v>
@@ -2405,28 +2405,28 @@
         <v>1831.9</v>
       </c>
       <c r="M12">
-        <v>83.34408199999999</v>
+        <v>91.67849019999998</v>
       </c>
       <c r="N12">
-        <v>1748.555918</v>
+        <v>1740.2215098</v>
       </c>
       <c r="O12">
-        <v>524.5667754</v>
+        <v>522.06645294</v>
       </c>
       <c r="P12">
-        <v>1223.9891426</v>
+        <v>1218.15505686</v>
       </c>
       <c r="Q12">
-        <v>1623.9891426</v>
+        <v>1618.15505686</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09440706995274004</v>
+        <v>0.09480119654797829</v>
       </c>
       <c r="T12">
-        <v>0.7072920937258056</v>
+        <v>0.7130271159151728</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.97996493620267</v>
+        <v>19.9817863056388</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08824616492770068</v>
+        <v>0.08800496689793533</v>
       </c>
       <c r="C13">
-        <v>15160.2613410492</v>
+        <v>15083.43489941015</v>
       </c>
       <c r="D13">
-        <v>15550.0953410492</v>
+        <v>15638.96289941015</v>
       </c>
       <c r="E13">
-        <v>-684.9660000000001</v>
+        <v>-519.2720000000002</v>
       </c>
       <c r="F13">
-        <v>1822.634</v>
+        <v>1988.328</v>
       </c>
       <c r="G13">
         <v>1432.8</v>
@@ -2487,28 +2487,28 @@
         <v>1831.9</v>
       </c>
       <c r="M13">
-        <v>91.67849019999998</v>
+        <v>100.0128984</v>
       </c>
       <c r="N13">
-        <v>1740.2215098</v>
+        <v>1731.8871016</v>
       </c>
       <c r="O13">
-        <v>522.06645294</v>
+        <v>519.56613048</v>
       </c>
       <c r="P13">
-        <v>1218.15505686</v>
+        <v>1212.32097112</v>
       </c>
       <c r="Q13">
-        <v>1618.15505686</v>
+        <v>1612.32097112</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09480119654797829</v>
+        <v>0.0952042805658356</v>
       </c>
       <c r="T13">
-        <v>0.7130271159151728</v>
+        <v>0.7188924795179347</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.9817863056388</v>
+        <v>18.31663744683556</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08800496689793533</v>
+        <v>0.08776376886816996</v>
       </c>
       <c r="C14">
-        <v>15083.43489941015</v>
+        <v>15007.63003808027</v>
       </c>
       <c r="D14">
-        <v>15638.96289941015</v>
+        <v>15728.85203808027</v>
       </c>
       <c r="E14">
-        <v>-519.2720000000002</v>
+        <v>-353.578</v>
       </c>
       <c r="F14">
-        <v>1988.328</v>
+        <v>2154.022</v>
       </c>
       <c r="G14">
         <v>1432.8</v>
@@ -2569,28 +2569,28 @@
         <v>1831.9</v>
       </c>
       <c r="M14">
-        <v>100.0128984</v>
+        <v>108.3473066</v>
       </c>
       <c r="N14">
-        <v>1731.8871016</v>
+        <v>1723.5526934</v>
       </c>
       <c r="O14">
-        <v>519.56613048</v>
+        <v>517.0658080200001</v>
       </c>
       <c r="P14">
-        <v>1212.32097112</v>
+        <v>1206.48688538</v>
       </c>
       <c r="Q14">
-        <v>1612.32097112</v>
+        <v>1606.48688538</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0952042805658356</v>
+        <v>0.09561663088295397</v>
       </c>
       <c r="T14">
-        <v>0.7188924795179347</v>
+        <v>0.7248926790655875</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.31663744683556</v>
+        <v>16.90766533554051</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08776376886816996</v>
+        <v>0.0875225708384046</v>
       </c>
       <c r="C15">
-        <v>15007.63003808027</v>
+        <v>14932.86447431564</v>
       </c>
       <c r="D15">
-        <v>15728.85203808027</v>
+        <v>15819.78047431564</v>
       </c>
       <c r="E15">
-        <v>-353.578</v>
+        <v>-187.884</v>
       </c>
       <c r="F15">
-        <v>2154.022</v>
+        <v>2319.716</v>
       </c>
       <c r="G15">
         <v>1432.8</v>
@@ -2651,28 +2651,28 @@
         <v>1831.9</v>
       </c>
       <c r="M15">
-        <v>108.3473066</v>
+        <v>116.6817148</v>
       </c>
       <c r="N15">
-        <v>1723.5526934</v>
+        <v>1715.2182852</v>
       </c>
       <c r="O15">
-        <v>517.0658080200001</v>
+        <v>514.56548556</v>
       </c>
       <c r="P15">
-        <v>1206.48688538</v>
+        <v>1200.65279964</v>
       </c>
       <c r="Q15">
-        <v>1606.48688538</v>
+        <v>1600.65279964</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09561663088295397</v>
+        <v>0.09603857074233094</v>
       </c>
       <c r="T15">
-        <v>0.7248926790655875</v>
+        <v>0.7310324181376044</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.90766533554051</v>
+        <v>15.69997495443048</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0875225708384046</v>
+        <v>0.08728137280863923</v>
       </c>
       <c r="C16">
-        <v>14932.86447431564</v>
+        <v>14859.15633744819</v>
       </c>
       <c r="D16">
-        <v>15819.78047431564</v>
+        <v>15911.76633744819</v>
       </c>
       <c r="E16">
-        <v>-187.884</v>
+        <v>-22.19000000000005</v>
       </c>
       <c r="F16">
-        <v>2319.716</v>
+        <v>2485.41</v>
       </c>
       <c r="G16">
         <v>1432.8</v>
@@ -2733,28 +2733,28 @@
         <v>1831.9</v>
       </c>
       <c r="M16">
-        <v>116.6817148</v>
+        <v>125.016123</v>
       </c>
       <c r="N16">
-        <v>1715.2182852</v>
+        <v>1706.883877</v>
       </c>
       <c r="O16">
-        <v>514.56548556</v>
+        <v>512.0651631000001</v>
       </c>
       <c r="P16">
-        <v>1200.65279964</v>
+        <v>1194.8187139</v>
       </c>
       <c r="Q16">
-        <v>1600.65279964</v>
+        <v>1594.8187139</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09603857074233094</v>
+        <v>0.09647043859839911</v>
       </c>
       <c r="T16">
-        <v>0.7310324181376044</v>
+        <v>0.7373166216583747</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.69997495443048</v>
+        <v>14.65330995746845</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08728137280863923</v>
+        <v>0.08704017477887388</v>
       </c>
       <c r="C17">
-        <v>14859.15633744819</v>
+        <v>14786.52418093594</v>
       </c>
       <c r="D17">
-        <v>15911.76633744819</v>
+        <v>16004.82818093594</v>
       </c>
       <c r="E17">
-        <v>-22.19000000000051</v>
+        <v>143.5039999999999</v>
       </c>
       <c r="F17">
-        <v>2485.409999999999</v>
+        <v>2651.104</v>
       </c>
       <c r="G17">
         <v>1432.8</v>
@@ -2815,28 +2815,28 @@
         <v>1831.9</v>
       </c>
       <c r="M17">
-        <v>125.016123</v>
+        <v>133.3505312</v>
       </c>
       <c r="N17">
-        <v>1706.883877</v>
+        <v>1698.5494688</v>
       </c>
       <c r="O17">
-        <v>512.0651631000001</v>
+        <v>509.56484064</v>
       </c>
       <c r="P17">
-        <v>1194.8187139</v>
+        <v>1188.98462816</v>
       </c>
       <c r="Q17">
-        <v>1594.8187139</v>
+        <v>1588.98462816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09647043859839911</v>
+        <v>0.09691258902246891</v>
       </c>
       <c r="T17">
-        <v>0.7373166216583747</v>
+        <v>0.7437504490724967</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.65330995746845</v>
+        <v>13.73747808512667</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08704017477887388</v>
+        <v>0.08679897674910853</v>
       </c>
       <c r="C18">
-        <v>14786.52418093594</v>
+        <v>14714.98699483883</v>
       </c>
       <c r="D18">
-        <v>16004.82818093594</v>
+        <v>16098.98499483883</v>
       </c>
       <c r="E18">
-        <v>143.5039999999999</v>
+        <v>309.1979999999999</v>
       </c>
       <c r="F18">
-        <v>2651.104</v>
+        <v>2816.798</v>
       </c>
       <c r="G18">
         <v>1432.8</v>
@@ -2897,28 +2897,28 @@
         <v>1831.9</v>
       </c>
       <c r="M18">
-        <v>133.3505312</v>
+        <v>141.6849394</v>
       </c>
       <c r="N18">
-        <v>1698.5494688</v>
+        <v>1690.2150606</v>
       </c>
       <c r="O18">
-        <v>509.56484064</v>
+        <v>507.06451818</v>
       </c>
       <c r="P18">
-        <v>1188.98462816</v>
+        <v>1183.15054242</v>
       </c>
       <c r="Q18">
-        <v>1588.98462816</v>
+        <v>1583.15054242</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09691258902246891</v>
+        <v>0.09736539367362473</v>
       </c>
       <c r="T18">
-        <v>0.7437504490724967</v>
+        <v>0.7503393084725012</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.73747808512667</v>
+        <v>12.92939113894275</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08679897674910853</v>
+        <v>0.08655777871934317</v>
       </c>
       <c r="C19">
-        <v>14714.98699483883</v>
+        <v>14644.56421873736</v>
       </c>
       <c r="D19">
-        <v>16098.98499483883</v>
+        <v>16194.25621873736</v>
       </c>
       <c r="E19">
-        <v>309.1979999999999</v>
+        <v>474.8919999999998</v>
       </c>
       <c r="F19">
-        <v>2816.798</v>
+        <v>2982.492</v>
       </c>
       <c r="G19">
         <v>1432.8</v>
@@ -2979,28 +2979,28 @@
         <v>1831.9</v>
       </c>
       <c r="M19">
-        <v>141.6849394</v>
+        <v>150.0193476</v>
       </c>
       <c r="N19">
-        <v>1690.2150606</v>
+        <v>1681.8806524</v>
       </c>
       <c r="O19">
-        <v>507.06451818</v>
+        <v>504.56419572</v>
       </c>
       <c r="P19">
-        <v>1183.15054242</v>
+        <v>1177.31645668</v>
       </c>
       <c r="Q19">
-        <v>1583.15054242</v>
+        <v>1577.31645668</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09736539367362473</v>
+        <v>0.0978292423406624</v>
       </c>
       <c r="T19">
-        <v>0.7503393084725012</v>
+        <v>0.7570888717603104</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.92939113894275</v>
+        <v>12.21109163122371</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08655777871934317</v>
+        <v>0.08631658068957782</v>
       </c>
       <c r="C20">
-        <v>14644.56421873736</v>
+        <v>14575.27575511273</v>
       </c>
       <c r="D20">
-        <v>16194.25621873736</v>
+        <v>16290.66175511273</v>
       </c>
       <c r="E20">
-        <v>474.8919999999994</v>
+        <v>640.5859999999998</v>
       </c>
       <c r="F20">
-        <v>2982.491999999999</v>
+        <v>3148.186</v>
       </c>
       <c r="G20">
         <v>1432.8</v>
@@ -3061,28 +3061,28 @@
         <v>1831.9</v>
       </c>
       <c r="M20">
-        <v>150.0193475999999</v>
+        <v>158.3537558</v>
       </c>
       <c r="N20">
-        <v>1681.8806524</v>
+        <v>1673.5462442</v>
       </c>
       <c r="O20">
-        <v>504.56419572</v>
+        <v>502.06387326</v>
       </c>
       <c r="P20">
-        <v>1177.31645668</v>
+        <v>1171.48237094</v>
       </c>
       <c r="Q20">
-        <v>1577.31645668</v>
+        <v>1571.48237094</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0978292423406624</v>
+        <v>0.09830454406120717</v>
       </c>
       <c r="T20">
-        <v>0.7570888717603104</v>
+        <v>0.7640050909317694</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.21109163122371</v>
+        <v>11.56840259800141</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08631658068957782</v>
+        <v>0.08607538265981246</v>
       </c>
       <c r="C21">
-        <v>14575.27575511273</v>
+        <v>14507.14198320779</v>
       </c>
       <c r="D21">
-        <v>16290.66175511273</v>
+        <v>16388.22198320779</v>
       </c>
       <c r="E21">
-        <v>640.5859999999998</v>
+        <v>806.2799999999997</v>
       </c>
       <c r="F21">
-        <v>3148.186</v>
+        <v>3313.88</v>
       </c>
       <c r="G21">
         <v>1432.8</v>
@@ -3143,28 +3143,28 @@
         <v>1831.9</v>
       </c>
       <c r="M21">
-        <v>158.3537558</v>
+        <v>166.688164</v>
       </c>
       <c r="N21">
-        <v>1673.5462442</v>
+        <v>1665.211836</v>
       </c>
       <c r="O21">
-        <v>502.06387326</v>
+        <v>499.5635508</v>
       </c>
       <c r="P21">
-        <v>1171.48237094</v>
+        <v>1165.6482852</v>
       </c>
       <c r="Q21">
-        <v>1571.48237094</v>
+        <v>1565.6482852</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09830454406120717</v>
+        <v>0.09879172832476557</v>
       </c>
       <c r="T21">
-        <v>0.7640050909317694</v>
+        <v>0.771094215582515</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.56840259800141</v>
+        <v>10.98998246810134</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08607538265981246</v>
+        <v>0.08583418463004711</v>
       </c>
       <c r="C22">
-        <v>14507.14198320779</v>
+        <v>14440.18377338897</v>
       </c>
       <c r="D22">
-        <v>16388.22198320779</v>
+        <v>16486.95777338897</v>
       </c>
       <c r="E22">
-        <v>806.2799999999997</v>
+        <v>971.9740000000002</v>
       </c>
       <c r="F22">
-        <v>3313.88</v>
+        <v>3479.574</v>
       </c>
       <c r="G22">
         <v>1432.8</v>
@@ -3225,28 +3225,28 @@
         <v>1831.9</v>
       </c>
       <c r="M22">
-        <v>166.688164</v>
+        <v>175.0225722</v>
       </c>
       <c r="N22">
-        <v>1665.211836</v>
+        <v>1656.8774278</v>
       </c>
       <c r="O22">
-        <v>499.5635508</v>
+        <v>497.06322834</v>
       </c>
       <c r="P22">
-        <v>1165.6482852</v>
+        <v>1159.81419946</v>
       </c>
       <c r="Q22">
-        <v>1565.6482852</v>
+        <v>1559.81419946</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09879172832476557</v>
+        <v>0.09929124636714823</v>
       </c>
       <c r="T22">
-        <v>0.771094215582515</v>
+        <v>0.7783628117434059</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.98998246810134</v>
+        <v>10.46664996962032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08583418463004709</v>
+        <v>0.08559298660028174</v>
       </c>
       <c r="C23">
-        <v>14440.18377338897</v>
+        <v>14374.4225020306</v>
       </c>
       <c r="D23">
-        <v>16486.95777338897</v>
+        <v>16586.8905020306</v>
       </c>
       <c r="E23">
-        <v>971.9739999999997</v>
+        <v>1137.668</v>
       </c>
       <c r="F23">
-        <v>3479.574</v>
+        <v>3645.268</v>
       </c>
       <c r="G23">
         <v>1432.8</v>
@@ -3307,28 +3307,28 @@
         <v>1831.9</v>
       </c>
       <c r="M23">
-        <v>175.0225722</v>
+        <v>183.3569804</v>
       </c>
       <c r="N23">
-        <v>1656.8774278</v>
+        <v>1648.5430196</v>
       </c>
       <c r="O23">
-        <v>497.06322834</v>
+        <v>494.56290588</v>
       </c>
       <c r="P23">
-        <v>1159.81419946</v>
+        <v>1153.98011372</v>
       </c>
       <c r="Q23">
-        <v>1559.81419946</v>
+        <v>1553.98011372</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09929124636714821</v>
+        <v>0.09980357256446376</v>
       </c>
       <c r="T23">
-        <v>0.7783628117434058</v>
+        <v>0.7858177821648324</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.46664996962032</v>
+        <v>9.990893152819398</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08559298660028174</v>
+        <v>0.08535178857051638</v>
       </c>
       <c r="C24">
-        <v>14374.4225020306</v>
+        <v>14309.8800669438</v>
       </c>
       <c r="D24">
-        <v>16586.8905020306</v>
+        <v>16688.0420669438</v>
       </c>
       <c r="E24">
-        <v>1137.668</v>
+        <v>1303.362</v>
       </c>
       <c r="F24">
-        <v>3645.268</v>
+        <v>3810.962</v>
       </c>
       <c r="G24">
         <v>1432.8</v>
@@ -3389,28 +3389,28 @@
         <v>1831.9</v>
       </c>
       <c r="M24">
-        <v>183.3569804</v>
+        <v>191.6913886</v>
       </c>
       <c r="N24">
-        <v>1648.5430196</v>
+        <v>1640.2086114</v>
       </c>
       <c r="O24">
-        <v>494.56290588</v>
+        <v>492.06258342</v>
       </c>
       <c r="P24">
-        <v>1153.98011372</v>
+        <v>1148.14602798</v>
       </c>
       <c r="Q24">
-        <v>1553.98011372</v>
+        <v>1548.14602798</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09980357256446376</v>
+        <v>0.1003292059357355</v>
       </c>
       <c r="T24">
-        <v>0.7858177821648324</v>
+        <v>0.7934663881816207</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.990893152819398</v>
+        <v>9.556506494001162</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08535178857051638</v>
+        <v>0.08511059054075101</v>
       </c>
       <c r="C25">
-        <v>14309.8800669438</v>
+        <v>14246.57890337336</v>
       </c>
       <c r="D25">
-        <v>16688.0420669438</v>
+        <v>16790.43490337336</v>
       </c>
       <c r="E25">
-        <v>1303.362</v>
+        <v>1469.056</v>
       </c>
       <c r="F25">
-        <v>3810.962</v>
+        <v>3976.656</v>
       </c>
       <c r="G25">
         <v>1432.8</v>
@@ -3471,28 +3471,28 @@
         <v>1831.9</v>
       </c>
       <c r="M25">
-        <v>191.6913886</v>
+        <v>200.0257968</v>
       </c>
       <c r="N25">
-        <v>1640.2086114</v>
+        <v>1631.8742032</v>
       </c>
       <c r="O25">
-        <v>492.06258342</v>
+        <v>489.56226096</v>
       </c>
       <c r="P25">
-        <v>1148.14602798</v>
+        <v>1142.31194224</v>
       </c>
       <c r="Q25">
-        <v>1548.14602798</v>
+        <v>1542.31194224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1003292059357355</v>
+        <v>0.1008686717641461</v>
       </c>
       <c r="T25">
-        <v>0.7934663881816207</v>
+        <v>0.801316273304114</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.556506494001162</v>
+        <v>9.158318723417779</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08511059054075101</v>
+        <v>0.08486939251098567</v>
       </c>
       <c r="C26">
-        <v>14246.57890337336</v>
+        <v>14184.5420005872</v>
       </c>
       <c r="D26">
-        <v>16790.43490337336</v>
+        <v>16894.0920005872</v>
       </c>
       <c r="E26">
-        <v>1469.056</v>
+        <v>1634.75</v>
       </c>
       <c r="F26">
-        <v>3976.655999999999</v>
+        <v>4142.349999999999</v>
       </c>
       <c r="G26">
         <v>1432.8</v>
@@ -3553,28 +3553,28 @@
         <v>1831.9</v>
       </c>
       <c r="M26">
-        <v>200.0257968</v>
+        <v>208.360205</v>
       </c>
       <c r="N26">
-        <v>1631.8742032</v>
+        <v>1623.539795</v>
       </c>
       <c r="O26">
-        <v>489.56226096</v>
+        <v>487.0619385</v>
       </c>
       <c r="P26">
-        <v>1142.31194224</v>
+        <v>1136.4778565</v>
       </c>
       <c r="Q26">
-        <v>1542.31194224</v>
+        <v>1536.4778565</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1008686717641461</v>
+        <v>0.1014225233479809</v>
       </c>
       <c r="T26">
-        <v>0.801316273304114</v>
+        <v>0.8093754886965405</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.15831872341778</v>
+        <v>8.79198597448107</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08486939251098567</v>
+        <v>0.0849011944812203</v>
       </c>
       <c r="C27">
-        <v>14184.5420005872</v>
+        <v>14005.10761699861</v>
       </c>
       <c r="D27">
-        <v>16894.0920005872</v>
+        <v>16880.35161699861</v>
       </c>
       <c r="E27">
-        <v>1634.75</v>
+        <v>1800.444</v>
       </c>
       <c r="F27">
-        <v>4142.349999999999</v>
+        <v>4308.044</v>
       </c>
       <c r="G27">
         <v>1432.8</v>
@@ -3635,45 +3635,45 @@
         <v>1831.9</v>
       </c>
       <c r="M27">
-        <v>208.360205</v>
+        <v>223.1566792</v>
       </c>
       <c r="N27">
-        <v>1623.539795</v>
+        <v>1608.7433208</v>
       </c>
       <c r="O27">
-        <v>487.0619385</v>
+        <v>482.62299624</v>
       </c>
       <c r="P27">
-        <v>1136.4778565</v>
+        <v>1126.12032456</v>
       </c>
       <c r="Q27">
-        <v>1536.4778565</v>
+        <v>1526.12032456</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1014225233479809</v>
+        <v>0.1019913438935409</v>
       </c>
       <c r="T27">
-        <v>0.8093754886965405</v>
+        <v>0.8176525207211947</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>8.79198597448107</v>
+        <v>8.209030563491197</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0849011944812203</v>
+        <v>0.08467049645145494</v>
       </c>
       <c r="C28">
-        <v>14005.10761699861</v>
+        <v>13939.59921315254</v>
       </c>
       <c r="D28">
-        <v>16880.35161699861</v>
+        <v>16980.53721315254</v>
       </c>
       <c r="E28">
-        <v>1800.444</v>
+        <v>1966.137999999999</v>
       </c>
       <c r="F28">
-        <v>4308.044</v>
+        <v>4473.737999999999</v>
       </c>
       <c r="G28">
         <v>1432.8</v>
@@ -3717,28 +3717,28 @@
         <v>1831.9</v>
       </c>
       <c r="M28">
-        <v>223.1566792</v>
+        <v>231.7396284</v>
       </c>
       <c r="N28">
-        <v>1608.7433208</v>
+        <v>1600.1603716</v>
       </c>
       <c r="O28">
-        <v>482.62299624</v>
+        <v>480.04811148</v>
       </c>
       <c r="P28">
-        <v>1126.12032456</v>
+        <v>1120.11226012</v>
       </c>
       <c r="Q28">
-        <v>1526.12032456</v>
+        <v>1520.11226012</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1019913438935409</v>
+        <v>0.1025757485636369</v>
       </c>
       <c r="T28">
-        <v>0.8176525207211947</v>
+        <v>0.8261563207465243</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.209030563491197</v>
+        <v>7.904992394473005</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08467049645145494</v>
+        <v>0.08443979842168958</v>
       </c>
       <c r="C29">
-        <v>13939.59921315254</v>
+        <v>13875.28712091199</v>
       </c>
       <c r="D29">
-        <v>16980.53721315254</v>
+        <v>17081.919120912</v>
       </c>
       <c r="E29">
-        <v>1966.137999999999</v>
+        <v>2131.832</v>
       </c>
       <c r="F29">
-        <v>4473.737999999999</v>
+        <v>4639.432</v>
       </c>
       <c r="G29">
         <v>1432.8</v>
@@ -3799,28 +3799,28 @@
         <v>1831.9</v>
       </c>
       <c r="M29">
-        <v>231.7396284</v>
+        <v>240.3225776</v>
       </c>
       <c r="N29">
-        <v>1600.1603716</v>
+        <v>1591.5774224</v>
       </c>
       <c r="O29">
-        <v>480.04811148</v>
+        <v>477.47322672</v>
       </c>
       <c r="P29">
-        <v>1120.11226012</v>
+        <v>1114.10419568</v>
       </c>
       <c r="Q29">
-        <v>1520.11226012</v>
+        <v>1514.10419568</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1025757485636369</v>
+        <v>0.1031763866967911</v>
       </c>
       <c r="T29">
-        <v>0.8261563207465243</v>
+        <v>0.8348963374392242</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.904992394473005</v>
+        <v>7.62267123752754</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08443979842168958</v>
+        <v>0.08420910039192421</v>
       </c>
       <c r="C30">
-        <v>13875.28712091199</v>
+        <v>13812.19289663167</v>
       </c>
       <c r="D30">
-        <v>17081.919120912</v>
+        <v>17184.51889663167</v>
       </c>
       <c r="E30">
-        <v>2131.832</v>
+        <v>2297.526</v>
       </c>
       <c r="F30">
-        <v>4639.432</v>
+        <v>4805.126</v>
       </c>
       <c r="G30">
         <v>1432.8</v>
@@ -3881,28 +3881,28 @@
         <v>1831.9</v>
       </c>
       <c r="M30">
-        <v>240.3225776</v>
+        <v>248.9055268</v>
       </c>
       <c r="N30">
-        <v>1591.5774224</v>
+        <v>1582.9944732</v>
       </c>
       <c r="O30">
-        <v>477.47322672</v>
+        <v>474.89834196</v>
       </c>
       <c r="P30">
-        <v>1114.10419568</v>
+        <v>1108.09613124</v>
       </c>
       <c r="Q30">
-        <v>1514.10419568</v>
+        <v>1508.09613124</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1031763866967911</v>
+        <v>0.1037939442139778</v>
       </c>
       <c r="T30">
-        <v>0.8348963374392242</v>
+        <v>0.8438825517852396</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.62267123752754</v>
+        <v>7.359820505199004</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08420910039192421</v>
+        <v>0.08397840236215885</v>
       </c>
       <c r="C31">
-        <v>13812.19289663167</v>
+        <v>13750.33861769469</v>
       </c>
       <c r="D31">
-        <v>17184.51889663167</v>
+        <v>17288.35861769469</v>
       </c>
       <c r="E31">
-        <v>2297.525999999999</v>
+        <v>2463.219999999999</v>
       </c>
       <c r="F31">
-        <v>4805.125999999999</v>
+        <v>4970.819999999999</v>
       </c>
       <c r="G31">
         <v>1432.8</v>
@@ -3963,28 +3963,28 @@
         <v>1831.9</v>
       </c>
       <c r="M31">
-        <v>248.9055268</v>
+        <v>257.4884759999999</v>
       </c>
       <c r="N31">
-        <v>1582.9944732</v>
+        <v>1574.411524</v>
       </c>
       <c r="O31">
-        <v>474.89834196</v>
+        <v>472.3234572</v>
       </c>
       <c r="P31">
-        <v>1108.09613124</v>
+        <v>1102.0880668</v>
       </c>
       <c r="Q31">
-        <v>1508.09613124</v>
+        <v>1502.0880668</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1037939442139778</v>
+        <v>0.1044291462316555</v>
       </c>
       <c r="T31">
-        <v>0.8438825517852396</v>
+        <v>0.8531255151125697</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.359820505199004</v>
+        <v>7.114493155025705</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08397840236215885</v>
+        <v>0.08374770433239349</v>
       </c>
       <c r="C32">
-        <v>13750.33861769469</v>
+        <v>13689.7468983503</v>
       </c>
       <c r="D32">
-        <v>17288.35861769469</v>
+        <v>17393.4608983503</v>
       </c>
       <c r="E32">
-        <v>2463.219999999999</v>
+        <v>2628.913999999999</v>
       </c>
       <c r="F32">
-        <v>4970.819999999999</v>
+        <v>5136.513999999999</v>
       </c>
       <c r="G32">
         <v>1432.8</v>
@@ -4045,28 +4045,28 @@
         <v>1831.9</v>
       </c>
       <c r="M32">
-        <v>257.4884759999999</v>
+        <v>266.0714252</v>
       </c>
       <c r="N32">
-        <v>1574.411524</v>
+        <v>1565.8285748</v>
       </c>
       <c r="O32">
-        <v>472.3234572</v>
+        <v>469.74857244</v>
       </c>
       <c r="P32">
-        <v>1102.0880668</v>
+        <v>1096.08000236</v>
       </c>
       <c r="Q32">
-        <v>1502.0880668</v>
+        <v>1496.08000236</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1044291462316555</v>
+        <v>0.1050827599020196</v>
       </c>
       <c r="T32">
-        <v>0.8531255151125697</v>
+        <v>0.8626363904204021</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.114493155025705</v>
+        <v>6.884993375831327</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08374770433239349</v>
+        <v>0.08389780630262812</v>
       </c>
       <c r="C33">
-        <v>13689.7468983503</v>
+        <v>13455.52420855376</v>
       </c>
       <c r="D33">
-        <v>17393.4608983503</v>
+        <v>17324.93220855376</v>
       </c>
       <c r="E33">
-        <v>2628.913999999999</v>
+        <v>2794.608</v>
       </c>
       <c r="F33">
-        <v>5136.513999999999</v>
+        <v>5302.208</v>
       </c>
       <c r="G33">
         <v>1432.8</v>
@@ -4127,45 +4127,45 @@
         <v>1831.9</v>
       </c>
       <c r="M33">
-        <v>266.0714252</v>
+        <v>283.668128</v>
       </c>
       <c r="N33">
-        <v>1565.8285748</v>
+        <v>1548.231872</v>
       </c>
       <c r="O33">
-        <v>469.74857244</v>
+        <v>464.4695616</v>
       </c>
       <c r="P33">
-        <v>1096.08000236</v>
+        <v>1083.7623104</v>
       </c>
       <c r="Q33">
-        <v>1496.08000236</v>
+        <v>1483.7623104</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1050827599020196</v>
+        <v>0.1057555975038649</v>
       </c>
       <c r="T33">
-        <v>0.8626363904204021</v>
+        <v>0.8724269973549355</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.884993375831327</v>
+        <v>6.457898576466088</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08389780630262812</v>
+        <v>0.08367900827286279</v>
       </c>
       <c r="C34">
-        <v>13455.52420855376</v>
+        <v>13389.90307756193</v>
       </c>
       <c r="D34">
-        <v>17324.93220855376</v>
+        <v>17425.00507756193</v>
       </c>
       <c r="E34">
-        <v>2794.608</v>
+        <v>2960.301999999999</v>
       </c>
       <c r="F34">
-        <v>5302.208</v>
+        <v>5467.901999999999</v>
       </c>
       <c r="G34">
         <v>1432.8</v>
@@ -4209,28 +4209,28 @@
         <v>1831.9</v>
       </c>
       <c r="M34">
-        <v>283.668128</v>
+        <v>292.5327569999999</v>
       </c>
       <c r="N34">
-        <v>1548.231872</v>
+        <v>1539.367243</v>
       </c>
       <c r="O34">
-        <v>464.4695616</v>
+        <v>461.8101729</v>
       </c>
       <c r="P34">
-        <v>1083.7623104</v>
+        <v>1077.5570701</v>
       </c>
       <c r="Q34">
-        <v>1483.7623104</v>
+        <v>1477.5570701</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1057555975038649</v>
+        <v>0.106448519810243</v>
       </c>
       <c r="T34">
-        <v>0.8724269973549355</v>
+        <v>0.882509861212888</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.457898576466088</v>
+        <v>6.262204680209541</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08367900827286279</v>
+        <v>0.08346021024309741</v>
       </c>
       <c r="C35">
-        <v>13389.90307756193</v>
+        <v>13325.44475189864</v>
       </c>
       <c r="D35">
-        <v>17425.00507756193</v>
+        <v>17526.24075189864</v>
       </c>
       <c r="E35">
-        <v>2960.301999999999</v>
+        <v>3125.996</v>
       </c>
       <c r="F35">
-        <v>5467.901999999999</v>
+        <v>5633.596</v>
       </c>
       <c r="G35">
         <v>1432.8</v>
@@ -4291,28 +4291,28 @@
         <v>1831.9</v>
       </c>
       <c r="M35">
-        <v>292.5327569999999</v>
+        <v>301.397386</v>
       </c>
       <c r="N35">
-        <v>1539.367243</v>
+        <v>1530.502614</v>
       </c>
       <c r="O35">
-        <v>461.8101729</v>
+        <v>459.1507842</v>
       </c>
       <c r="P35">
-        <v>1077.5570701</v>
+        <v>1071.3518298</v>
       </c>
       <c r="Q35">
-        <v>1477.5570701</v>
+        <v>1471.3518298</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.106448519810243</v>
+        <v>0.1071624397622688</v>
       </c>
       <c r="T35">
-        <v>0.882509861212888</v>
+        <v>0.892898266399869</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.262204680209541</v>
+        <v>6.078022189615142</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08346021024309741</v>
+        <v>0.08324141221333206</v>
       </c>
       <c r="C36">
-        <v>13325.44475189864</v>
+        <v>13262.16961697401</v>
       </c>
       <c r="D36">
-        <v>17526.24075189864</v>
+        <v>17628.65961697401</v>
       </c>
       <c r="E36">
-        <v>3125.996</v>
+        <v>3291.69</v>
       </c>
       <c r="F36">
-        <v>5633.596</v>
+        <v>5799.29</v>
       </c>
       <c r="G36">
         <v>1432.8</v>
@@ -4373,28 +4373,28 @@
         <v>1831.9</v>
       </c>
       <c r="M36">
-        <v>301.397386</v>
+        <v>310.262015</v>
       </c>
       <c r="N36">
-        <v>1530.502614</v>
+        <v>1521.637985</v>
       </c>
       <c r="O36">
-        <v>459.1507842</v>
+        <v>456.4913955</v>
       </c>
       <c r="P36">
-        <v>1071.3518298</v>
+        <v>1065.1465895</v>
       </c>
       <c r="Q36">
-        <v>1471.3518298</v>
+        <v>1465.1465895</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1071624397622688</v>
+        <v>0.1078983264820493</v>
       </c>
       <c r="T36">
-        <v>0.892898266399869</v>
+        <v>0.9036063148233726</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.078022189615142</v>
+        <v>5.904364412768994</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08324141221333206</v>
+        <v>0.08302261418356671</v>
       </c>
       <c r="C37">
-        <v>13262.16961697401</v>
+        <v>13200.09853750764</v>
       </c>
       <c r="D37">
-        <v>17628.65961697401</v>
+        <v>17732.28253750764</v>
       </c>
       <c r="E37">
-        <v>3291.69</v>
+        <v>3457.384</v>
       </c>
       <c r="F37">
-        <v>5799.29</v>
+        <v>5964.983999999999</v>
       </c>
       <c r="G37">
         <v>1432.8</v>
@@ -4455,28 +4455,28 @@
         <v>1831.9</v>
       </c>
       <c r="M37">
-        <v>310.262015</v>
+        <v>319.1266439999999</v>
       </c>
       <c r="N37">
-        <v>1521.637985</v>
+        <v>1512.773356</v>
       </c>
       <c r="O37">
-        <v>456.4913955</v>
+        <v>453.8320068</v>
       </c>
       <c r="P37">
-        <v>1065.1465895</v>
+        <v>1058.9413492</v>
       </c>
       <c r="Q37">
-        <v>1465.1465895</v>
+        <v>1458.9413492</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1078983264820493</v>
+        <v>0.108657209661823</v>
       </c>
       <c r="T37">
-        <v>0.9036063148233726</v>
+        <v>0.9146489897601108</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.904364412768994</v>
+        <v>5.740354290192079</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08302261418356671</v>
+        <v>0.08280381615380134</v>
       </c>
       <c r="C38">
-        <v>13200.09853750764</v>
+        <v>13139.25287169901</v>
       </c>
       <c r="D38">
-        <v>17732.28253750764</v>
+        <v>17837.13087169901</v>
       </c>
       <c r="E38">
-        <v>3457.383999999999</v>
+        <v>3623.077999999999</v>
       </c>
       <c r="F38">
-        <v>5964.983999999999</v>
+        <v>6130.677999999999</v>
       </c>
       <c r="G38">
         <v>1432.8</v>
@@ -4537,28 +4537,28 @@
         <v>1831.9</v>
       </c>
       <c r="M38">
-        <v>319.1266439999999</v>
+        <v>327.9912729999999</v>
       </c>
       <c r="N38">
-        <v>1512.773356</v>
+        <v>1503.908727</v>
       </c>
       <c r="O38">
-        <v>453.8320068</v>
+        <v>451.1726181000001</v>
       </c>
       <c r="P38">
-        <v>1058.9413492</v>
+        <v>1052.7361089</v>
       </c>
       <c r="Q38">
-        <v>1458.9413492</v>
+        <v>1452.7361089</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.108657209661823</v>
+        <v>0.1094401843711132</v>
       </c>
       <c r="T38">
-        <v>0.9146489897601108</v>
+        <v>0.9260422258059516</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.740354290192079</v>
+        <v>5.585209579646348</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08280381615380134</v>
+        <v>0.08279781812403597</v>
       </c>
       <c r="C39">
-        <v>13139.25287169901</v>
+        <v>12976.45060011225</v>
       </c>
       <c r="D39">
-        <v>17837.13087169901</v>
+        <v>17840.02260011225</v>
       </c>
       <c r="E39">
-        <v>3623.077999999999</v>
+        <v>3788.771999999999</v>
       </c>
       <c r="F39">
-        <v>6130.677999999999</v>
+        <v>6296.371999999999</v>
       </c>
       <c r="G39">
         <v>1432.8</v>
@@ -4619,45 +4619,45 @@
         <v>1831.9</v>
       </c>
       <c r="M39">
-        <v>327.9912729999999</v>
+        <v>341.8929996</v>
       </c>
       <c r="N39">
-        <v>1503.908727</v>
+        <v>1490.0070004</v>
       </c>
       <c r="O39">
-        <v>451.1726181000001</v>
+        <v>447.00210012</v>
       </c>
       <c r="P39">
-        <v>1052.7361089</v>
+        <v>1043.00490028</v>
       </c>
       <c r="Q39">
-        <v>1452.7361089</v>
+        <v>1443.00490028</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1094401843711132</v>
+        <v>0.1102484163290903</v>
       </c>
       <c r="T39">
-        <v>0.9260422258059516</v>
+        <v>0.9378029855952068</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>5.585209579646348</v>
+        <v>5.358109122278735</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08279781812403597</v>
+        <v>0.08258462009427063</v>
       </c>
       <c r="C40">
-        <v>12976.45060011225</v>
+        <v>12914.15464145577</v>
       </c>
       <c r="D40">
-        <v>17840.02260011225</v>
+        <v>17943.42064145577</v>
       </c>
       <c r="E40">
-        <v>3788.771999999999</v>
+        <v>3954.466</v>
       </c>
       <c r="F40">
-        <v>6296.371999999999</v>
+        <v>6462.066</v>
       </c>
       <c r="G40">
         <v>1432.8</v>
@@ -4701,28 +4701,28 @@
         <v>1831.9</v>
       </c>
       <c r="M40">
-        <v>341.8929996</v>
+        <v>350.8901838</v>
       </c>
       <c r="N40">
-        <v>1490.0070004</v>
+        <v>1481.0098162</v>
       </c>
       <c r="O40">
-        <v>447.00210012</v>
+        <v>444.30294486</v>
       </c>
       <c r="P40">
-        <v>1043.00490028</v>
+        <v>1036.70687134</v>
       </c>
       <c r="Q40">
-        <v>1443.00490028</v>
+        <v>1436.70687134</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1102484163290903</v>
+        <v>0.1110831476955256</v>
       </c>
       <c r="T40">
-        <v>0.9378029855952068</v>
+        <v>0.949949344066077</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.358109122278735</v>
+        <v>5.220721708886973</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08258462009427063</v>
+        <v>0.08237142206450526</v>
       </c>
       <c r="C41">
-        <v>12914.15464145577</v>
+        <v>12853.06422841124</v>
       </c>
       <c r="D41">
-        <v>17943.42064145577</v>
+        <v>18048.02422841124</v>
       </c>
       <c r="E41">
-        <v>3954.466</v>
+        <v>4120.16</v>
       </c>
       <c r="F41">
-        <v>6462.066</v>
+        <v>6627.759999999999</v>
       </c>
       <c r="G41">
         <v>1432.8</v>
@@ -4783,28 +4783,28 @@
         <v>1831.9</v>
       </c>
       <c r="M41">
-        <v>350.8901838</v>
+        <v>359.887368</v>
       </c>
       <c r="N41">
-        <v>1481.0098162</v>
+        <v>1472.012632</v>
       </c>
       <c r="O41">
-        <v>444.30294486</v>
+        <v>441.6037896</v>
       </c>
       <c r="P41">
-        <v>1036.70687134</v>
+        <v>1030.4088424</v>
       </c>
       <c r="Q41">
-        <v>1436.70687134</v>
+        <v>1430.4088424</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1110831476955256</v>
+        <v>0.1119457034408421</v>
       </c>
       <c r="T41">
-        <v>0.949949344066077</v>
+        <v>0.9625005811526428</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.220721708886973</v>
+        <v>5.0902036661648</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08237142206450526</v>
+        <v>0.08215822403473991</v>
       </c>
       <c r="C42">
-        <v>12853.06422841124</v>
+        <v>12793.20056828092</v>
       </c>
       <c r="D42">
-        <v>18048.02422841124</v>
+        <v>18153.85456828092</v>
       </c>
       <c r="E42">
-        <v>4120.16</v>
+        <v>4285.853999999999</v>
       </c>
       <c r="F42">
-        <v>6627.759999999999</v>
+        <v>6793.454</v>
       </c>
       <c r="G42">
         <v>1432.8</v>
@@ -4865,28 +4865,28 @@
         <v>1831.9</v>
       </c>
       <c r="M42">
-        <v>359.887368</v>
+        <v>368.8845522</v>
       </c>
       <c r="N42">
-        <v>1472.012632</v>
+        <v>1463.0154478</v>
       </c>
       <c r="O42">
-        <v>441.6037896</v>
+        <v>438.90463434</v>
       </c>
       <c r="P42">
-        <v>1030.4088424</v>
+        <v>1024.11081346</v>
       </c>
       <c r="Q42">
-        <v>1430.4088424</v>
+        <v>1424.11081346</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1119457034408421</v>
+        <v>0.1128374983639659</v>
       </c>
       <c r="T42">
-        <v>0.9625005811526428</v>
+        <v>0.9754772839031599</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.0902036661648</v>
+        <v>4.96605235723395</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08215822403473991</v>
+        <v>0.08194502600497455</v>
       </c>
       <c r="C43">
-        <v>12793.20056828092</v>
+        <v>12734.58536872422</v>
       </c>
       <c r="D43">
-        <v>18153.85456828092</v>
+        <v>18260.93336872422</v>
       </c>
       <c r="E43">
-        <v>4285.853999999999</v>
+        <v>4451.548000000001</v>
       </c>
       <c r="F43">
-        <v>6793.454</v>
+        <v>6959.148</v>
       </c>
       <c r="G43">
         <v>1432.8</v>
@@ -4947,28 +4947,28 @@
         <v>1831.9</v>
       </c>
       <c r="M43">
-        <v>368.8845522</v>
+        <v>377.8817364</v>
       </c>
       <c r="N43">
-        <v>1463.0154478</v>
+        <v>1454.0182636</v>
       </c>
       <c r="O43">
-        <v>438.90463434</v>
+        <v>436.20547908</v>
       </c>
       <c r="P43">
-        <v>1024.11081346</v>
+        <v>1017.81278452</v>
       </c>
       <c r="Q43">
-        <v>1424.11081346</v>
+        <v>1417.81278452</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1128374983639659</v>
+        <v>0.113760044836163</v>
       </c>
       <c r="T43">
-        <v>0.9754772839031599</v>
+        <v>0.9889014591623155</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.96605235723395</v>
+        <v>4.847813015395046</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08194502600497455</v>
+        <v>0.0817318279752092</v>
       </c>
       <c r="C44">
-        <v>12734.58536872422</v>
+        <v>12677.2408526017</v>
       </c>
       <c r="D44">
-        <v>18260.93336872422</v>
+        <v>18369.2828526017</v>
       </c>
       <c r="E44">
-        <v>4451.547999999999</v>
+        <v>4617.241999999998</v>
       </c>
       <c r="F44">
-        <v>6959.147999999999</v>
+        <v>7124.841999999999</v>
       </c>
       <c r="G44">
         <v>1432.8</v>
@@ -5029,28 +5029,28 @@
         <v>1831.9</v>
       </c>
       <c r="M44">
-        <v>377.8817364</v>
+        <v>386.8789206</v>
       </c>
       <c r="N44">
-        <v>1454.0182636</v>
+        <v>1445.0210794</v>
       </c>
       <c r="O44">
-        <v>436.20547908</v>
+        <v>433.50632382</v>
       </c>
       <c r="P44">
-        <v>1017.81278452</v>
+        <v>1011.51475558</v>
       </c>
       <c r="Q44">
-        <v>1417.81278452</v>
+        <v>1411.51475558</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.113760044836163</v>
+        <v>0.1147149613600161</v>
       </c>
       <c r="T44">
-        <v>0.9889014591623154</v>
+        <v>1.002796658114775</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.847813015395047</v>
+        <v>4.73507317782772</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0817318279752092</v>
+        <v>0.08151862994544384</v>
       </c>
       <c r="C45">
-        <v>12677.2408526017</v>
+        <v>12621.18977335087</v>
       </c>
       <c r="D45">
-        <v>18369.2828526017</v>
+        <v>18478.92577335087</v>
       </c>
       <c r="E45">
-        <v>4617.241999999998</v>
+        <v>4782.936</v>
       </c>
       <c r="F45">
-        <v>7124.841999999999</v>
+        <v>7290.535999999999</v>
       </c>
       <c r="G45">
         <v>1432.8</v>
@@ -5111,28 +5111,28 @@
         <v>1831.9</v>
       </c>
       <c r="M45">
-        <v>386.8789206</v>
+        <v>395.8761048</v>
       </c>
       <c r="N45">
-        <v>1445.0210794</v>
+        <v>1436.0238952</v>
       </c>
       <c r="O45">
-        <v>433.50632382</v>
+        <v>430.80716856</v>
       </c>
       <c r="P45">
-        <v>1011.51475558</v>
+        <v>1005.21672664</v>
       </c>
       <c r="Q45">
-        <v>1411.51475558</v>
+        <v>1405.21672664</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1147149613600161</v>
+        <v>0.1157039820454354</v>
       </c>
       <c r="T45">
-        <v>1.002796658114775</v>
+        <v>1.017188114172679</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.73507317782772</v>
+        <v>4.627457878331636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08151862994544384</v>
+        <v>0.08130543191567847</v>
       </c>
       <c r="C46">
-        <v>12621.18977335087</v>
+        <v>12566.4554309158</v>
       </c>
       <c r="D46">
-        <v>18478.92577335087</v>
+        <v>18589.88543091581</v>
       </c>
       <c r="E46">
-        <v>4782.936</v>
+        <v>4948.629999999999</v>
       </c>
       <c r="F46">
-        <v>7290.535999999999</v>
+        <v>7456.23</v>
       </c>
       <c r="G46">
         <v>1432.8</v>
@@ -5193,28 +5193,28 @@
         <v>1831.9</v>
       </c>
       <c r="M46">
-        <v>395.8761048</v>
+        <v>404.873289</v>
       </c>
       <c r="N46">
-        <v>1436.0238952</v>
+        <v>1427.026711</v>
       </c>
       <c r="O46">
-        <v>430.80716856</v>
+        <v>428.1080133</v>
       </c>
       <c r="P46">
-        <v>1005.21672664</v>
+        <v>998.9186976999999</v>
       </c>
       <c r="Q46">
-        <v>1405.21672664</v>
+        <v>1398.9186977</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1157039820454354</v>
+        <v>0.1167289671194154</v>
       </c>
       <c r="T46">
-        <v>1.017188114172679</v>
+        <v>1.032102895905417</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.627457878331636</v>
+        <v>4.524625481035376</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08130543191567847</v>
+        <v>0.08109223388591312</v>
       </c>
       <c r="C47">
-        <v>12566.4554309158</v>
+        <v>12513.0616882542</v>
       </c>
       <c r="D47">
-        <v>18589.88543091581</v>
+        <v>18702.1856882542</v>
       </c>
       <c r="E47">
-        <v>4948.629999999999</v>
+        <v>5114.323999999999</v>
       </c>
       <c r="F47">
-        <v>7456.23</v>
+        <v>7621.923999999999</v>
       </c>
       <c r="G47">
         <v>1432.8</v>
@@ -5275,28 +5275,28 @@
         <v>1831.9</v>
       </c>
       <c r="M47">
-        <v>404.873289</v>
+        <v>413.8704731999999</v>
       </c>
       <c r="N47">
-        <v>1427.026711</v>
+        <v>1418.0295268</v>
       </c>
       <c r="O47">
-        <v>428.1080133</v>
+        <v>425.40885804</v>
       </c>
       <c r="P47">
-        <v>998.9186976999999</v>
+        <v>992.6206687600002</v>
       </c>
       <c r="Q47">
-        <v>1398.9186977</v>
+        <v>1392.62066876</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1167289671194154</v>
+        <v>0.1177919146035428</v>
       </c>
       <c r="T47">
-        <v>1.032102895905417</v>
+        <v>1.047570076961588</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.524625481035376</v>
+        <v>4.426264057534608</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08109223388591312</v>
+        <v>0.08087903585614775</v>
       </c>
       <c r="C48">
-        <v>12513.0616882542</v>
+        <v>12461.0329884464</v>
       </c>
       <c r="D48">
-        <v>18702.1856882542</v>
+        <v>18815.8509884464</v>
       </c>
       <c r="E48">
-        <v>5114.323999999999</v>
+        <v>5280.018</v>
       </c>
       <c r="F48">
-        <v>7621.923999999999</v>
+        <v>7787.617999999999</v>
       </c>
       <c r="G48">
         <v>1432.8</v>
@@ -5357,28 +5357,28 @@
         <v>1831.9</v>
       </c>
       <c r="M48">
-        <v>413.8704731999999</v>
+        <v>422.8676574</v>
       </c>
       <c r="N48">
-        <v>1418.0295268</v>
+        <v>1409.0323426</v>
       </c>
       <c r="O48">
-        <v>425.40885804</v>
+        <v>422.70970278</v>
       </c>
       <c r="P48">
-        <v>992.6206687600002</v>
+        <v>986.3226398199999</v>
       </c>
       <c r="Q48">
-        <v>1392.62066876</v>
+        <v>1386.32263982</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1177919146035428</v>
+        <v>0.1188949733134863</v>
       </c>
       <c r="T48">
-        <v>1.047570076961588</v>
+        <v>1.063620925227427</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.426264057534608</v>
+        <v>4.332088226523233</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08087903585614775</v>
+        <v>0.0810018378263824</v>
       </c>
       <c r="C49">
-        <v>12461.0329884464</v>
+        <v>12229.69970039505</v>
       </c>
       <c r="D49">
-        <v>18815.8509884464</v>
+        <v>18750.21170039505</v>
       </c>
       <c r="E49">
-        <v>5280.018</v>
+        <v>5445.712</v>
       </c>
       <c r="F49">
-        <v>7787.617999999999</v>
+        <v>7953.312</v>
       </c>
       <c r="G49">
         <v>1432.8</v>
@@ -5439,45 +5439,45 @@
         <v>1831.9</v>
       </c>
       <c r="M49">
-        <v>422.8676574</v>
+        <v>439.8181536</v>
       </c>
       <c r="N49">
-        <v>1409.0323426</v>
+        <v>1392.0818464</v>
       </c>
       <c r="O49">
-        <v>422.70970278</v>
+        <v>417.62455392</v>
       </c>
       <c r="P49">
-        <v>986.3226398199999</v>
+        <v>974.4572924800001</v>
       </c>
       <c r="Q49">
-        <v>1386.32263982</v>
+        <v>1374.45729248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1188949733134863</v>
+        <v>0.1200404573584277</v>
       </c>
       <c r="T49">
-        <v>1.063620925227427</v>
+        <v>1.080289113811183</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.332088226523233</v>
+        <v>4.165130486328339</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0810018378263824</v>
+        <v>0.08079563979661704</v>
       </c>
       <c r="C50">
-        <v>12229.69970039505</v>
+        <v>12174.48394090656</v>
       </c>
       <c r="D50">
-        <v>18750.21170039505</v>
+        <v>18860.68994090656</v>
       </c>
       <c r="E50">
-        <v>5445.712</v>
+        <v>5611.405999999999</v>
       </c>
       <c r="F50">
-        <v>7953.311999999999</v>
+        <v>8119.005999999998</v>
       </c>
       <c r="G50">
         <v>1432.8</v>
@@ -5521,28 +5521,28 @@
         <v>1831.9</v>
       </c>
       <c r="M50">
-        <v>439.8181536</v>
+        <v>448.9810317999999</v>
       </c>
       <c r="N50">
-        <v>1392.0818464</v>
+        <v>1382.9189682</v>
       </c>
       <c r="O50">
-        <v>417.62455392</v>
+        <v>414.87569046</v>
       </c>
       <c r="P50">
-        <v>974.4572924800001</v>
+        <v>968.0432777400001</v>
       </c>
       <c r="Q50">
-        <v>1374.45729248</v>
+        <v>1368.04327774</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1200404573584277</v>
+        <v>0.1212308623463079</v>
       </c>
       <c r="T50">
-        <v>1.080289113811183</v>
+        <v>1.097610956849203</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.165130486328339</v>
+        <v>4.080127823342047</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08079563979661704</v>
+        <v>0.08058944176685168</v>
       </c>
       <c r="C51">
-        <v>12174.48394090656</v>
+        <v>12120.57779688578</v>
       </c>
       <c r="D51">
-        <v>18860.68994090656</v>
+        <v>18972.47779688578</v>
       </c>
       <c r="E51">
-        <v>5611.405999999999</v>
+        <v>5777.099999999999</v>
       </c>
       <c r="F51">
-        <v>8119.005999999998</v>
+        <v>8284.699999999999</v>
       </c>
       <c r="G51">
         <v>1432.8</v>
@@ -5603,28 +5603,28 @@
         <v>1831.9</v>
       </c>
       <c r="M51">
-        <v>448.9810317999999</v>
+        <v>458.1439099999999</v>
       </c>
       <c r="N51">
-        <v>1382.9189682</v>
+        <v>1373.75609</v>
       </c>
       <c r="O51">
-        <v>414.87569046</v>
+        <v>412.126827</v>
       </c>
       <c r="P51">
-        <v>968.0432777400001</v>
+        <v>961.629263</v>
       </c>
       <c r="Q51">
-        <v>1368.04327774</v>
+        <v>1361.629263</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1212308623463079</v>
+        <v>0.1224688835337034</v>
       </c>
       <c r="T51">
-        <v>1.097610956849203</v>
+        <v>1.115625673608745</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.080127823342047</v>
+        <v>3.998525266875206</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08058944176685168</v>
+        <v>0.08038324373708633</v>
       </c>
       <c r="C52">
-        <v>12120.57779688578</v>
+        <v>12068.00469356123</v>
       </c>
       <c r="D52">
-        <v>18972.47779688578</v>
+        <v>19085.59869356123</v>
       </c>
       <c r="E52">
-        <v>5777.099999999999</v>
+        <v>5942.793999999998</v>
       </c>
       <c r="F52">
-        <v>8284.699999999999</v>
+        <v>8450.393999999998</v>
       </c>
       <c r="G52">
         <v>1432.8</v>
@@ -5685,28 +5685,28 @@
         <v>1831.9</v>
       </c>
       <c r="M52">
-        <v>458.1439099999999</v>
+        <v>467.3067881999999</v>
       </c>
       <c r="N52">
-        <v>1373.75609</v>
+        <v>1364.5932118</v>
       </c>
       <c r="O52">
-        <v>412.126827</v>
+        <v>409.37796354</v>
       </c>
       <c r="P52">
-        <v>961.629263</v>
+        <v>955.2152482600001</v>
       </c>
       <c r="Q52">
-        <v>1361.629263</v>
+        <v>1355.21524826</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1224688835337034</v>
+        <v>0.1237574361981354</v>
       </c>
       <c r="T52">
-        <v>1.115625673608745</v>
+        <v>1.1343756849299</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.998525266875206</v>
+        <v>3.920122810661967</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08038324373708633</v>
+        <v>0.08017704570732095</v>
       </c>
       <c r="C53">
-        <v>12068.00469356123</v>
+        <v>12016.78861819181</v>
       </c>
       <c r="D53">
-        <v>19085.59869356123</v>
+        <v>19200.07661819182</v>
       </c>
       <c r="E53">
-        <v>5942.793999999998</v>
+        <v>6108.487999999999</v>
       </c>
       <c r="F53">
-        <v>8450.393999999998</v>
+        <v>8616.088</v>
       </c>
       <c r="G53">
         <v>1432.8</v>
@@ -5767,28 +5767,28 @@
         <v>1831.9</v>
       </c>
       <c r="M53">
-        <v>467.3067881999999</v>
+        <v>476.4696664</v>
       </c>
       <c r="N53">
-        <v>1364.5932118</v>
+        <v>1355.4303336</v>
       </c>
       <c r="O53">
-        <v>409.37796354</v>
+        <v>406.62910008</v>
       </c>
       <c r="P53">
-        <v>955.2152482600001</v>
+        <v>948.8012335200001</v>
       </c>
       <c r="Q53">
-        <v>1355.21524826</v>
+        <v>1348.80123352</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1237574361981354</v>
+        <v>0.1250996785569187</v>
       </c>
       <c r="T53">
-        <v>1.1343756849299</v>
+        <v>1.15390694672277</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.920122810661967</v>
+        <v>3.844735833533851</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08017704570732095</v>
+        <v>0.07997084767755561</v>
       </c>
       <c r="C54">
-        <v>12016.78861819181</v>
+        <v>11966.95413702416</v>
       </c>
       <c r="D54">
-        <v>19200.07661819182</v>
+        <v>19315.93613702416</v>
       </c>
       <c r="E54">
-        <v>6108.487999999999</v>
+        <v>6274.181999999999</v>
       </c>
       <c r="F54">
-        <v>8616.088</v>
+        <v>8781.781999999999</v>
       </c>
       <c r="G54">
         <v>1432.8</v>
@@ -5849,28 +5849,28 @@
         <v>1831.9</v>
       </c>
       <c r="M54">
-        <v>476.4696664</v>
+        <v>485.6325446</v>
       </c>
       <c r="N54">
-        <v>1355.4303336</v>
+        <v>1346.2674554</v>
       </c>
       <c r="O54">
-        <v>406.62910008</v>
+        <v>403.88023662</v>
       </c>
       <c r="P54">
-        <v>948.8012335200001</v>
+        <v>942.38721878</v>
       </c>
       <c r="Q54">
-        <v>1348.80123352</v>
+        <v>1342.38721878</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1250996785569187</v>
+        <v>0.1264990376118204</v>
       </c>
       <c r="T54">
-        <v>1.15390694672277</v>
+        <v>1.174269326038742</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.844735833533851</v>
+        <v>3.772193647995477</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07997084767755561</v>
+        <v>0.07976464964779023</v>
       </c>
       <c r="C55">
-        <v>11966.95413702416</v>
+        <v>11918.52641286773</v>
       </c>
       <c r="D55">
-        <v>19315.93613702416</v>
+        <v>19433.20241286773</v>
       </c>
       <c r="E55">
-        <v>6274.181999999999</v>
+        <v>6439.875999999998</v>
       </c>
       <c r="F55">
-        <v>8781.781999999999</v>
+        <v>8947.475999999999</v>
       </c>
       <c r="G55">
         <v>1432.8</v>
@@ -5931,28 +5931,28 @@
         <v>1831.9</v>
       </c>
       <c r="M55">
-        <v>485.6325446</v>
+        <v>494.7954227999999</v>
       </c>
       <c r="N55">
-        <v>1346.2674554</v>
+        <v>1337.1045772</v>
       </c>
       <c r="O55">
-        <v>403.88023662</v>
+        <v>401.1313731600001</v>
       </c>
       <c r="P55">
-        <v>942.38721878</v>
+        <v>935.9732040400002</v>
       </c>
       <c r="Q55">
-        <v>1342.38721878</v>
+        <v>1335.97320404</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1264990376118204</v>
+        <v>0.1279592383647614</v>
       </c>
       <c r="T55">
-        <v>1.174269326038742</v>
+        <v>1.195517026194537</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.772193647995477</v>
+        <v>3.702338210069635</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07976464964779023</v>
+        <v>0.07955845161802488</v>
       </c>
       <c r="C56">
-        <v>11918.52641286773</v>
+        <v>11871.53122331392</v>
       </c>
       <c r="D56">
-        <v>19433.20241286773</v>
+        <v>19551.90122331392</v>
       </c>
       <c r="E56">
-        <v>6439.875999999998</v>
+        <v>6605.57</v>
       </c>
       <c r="F56">
-        <v>8947.475999999999</v>
+        <v>9113.17</v>
       </c>
       <c r="G56">
         <v>1432.8</v>
@@ -6013,28 +6013,28 @@
         <v>1831.9</v>
       </c>
       <c r="M56">
-        <v>494.7954227999999</v>
+        <v>503.958301</v>
       </c>
       <c r="N56">
-        <v>1337.1045772</v>
+        <v>1327.941699</v>
       </c>
       <c r="O56">
-        <v>401.1313731600001</v>
+        <v>398.3825097</v>
       </c>
       <c r="P56">
-        <v>935.9732040400002</v>
+        <v>929.5591893000001</v>
       </c>
       <c r="Q56">
-        <v>1335.97320404</v>
+        <v>1329.5591893</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1279592383647614</v>
+        <v>0.1294843369289442</v>
       </c>
       <c r="T56">
-        <v>1.195517026194537</v>
+        <v>1.21770906857948</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.702338210069635</v>
+        <v>3.63502296988655</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07955845161802488</v>
+        <v>0.07935225358825954</v>
       </c>
       <c r="C57">
-        <v>11871.53122331392</v>
+        <v>11825.99497962703</v>
       </c>
       <c r="D57">
-        <v>19551.90122331392</v>
+        <v>19672.05897962703</v>
       </c>
       <c r="E57">
-        <v>6605.57</v>
+        <v>6771.263999999999</v>
       </c>
       <c r="F57">
-        <v>9113.17</v>
+        <v>9278.864</v>
       </c>
       <c r="G57">
         <v>1432.8</v>
@@ -6095,28 +6095,28 @@
         <v>1831.9</v>
       </c>
       <c r="M57">
-        <v>503.958301</v>
+        <v>513.1211792</v>
       </c>
       <c r="N57">
-        <v>1327.941699</v>
+        <v>1318.7788208</v>
       </c>
       <c r="O57">
-        <v>398.3825097</v>
+        <v>395.63364624</v>
       </c>
       <c r="P57">
-        <v>929.5591893000001</v>
+        <v>923.1451745600002</v>
       </c>
       <c r="Q57">
-        <v>1329.5591893</v>
+        <v>1323.14517456</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1294843369289442</v>
+        <v>0.1310787581551353</v>
       </c>
       <c r="T57">
-        <v>1.21770906857948</v>
+        <v>1.240909840163738</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.63502296988655</v>
+        <v>3.57011184542429</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07935225358825954</v>
+        <v>0.07914605555849416</v>
       </c>
       <c r="C58">
-        <v>11825.99497962703</v>
+        <v>11781.94474633617</v>
       </c>
       <c r="D58">
-        <v>19672.05897962703</v>
+        <v>19793.70274633617</v>
       </c>
       <c r="E58">
-        <v>6771.263999999999</v>
+        <v>6936.957999999999</v>
       </c>
       <c r="F58">
-        <v>9278.864</v>
+        <v>9444.557999999999</v>
       </c>
       <c r="G58">
         <v>1432.8</v>
@@ -6177,28 +6177,28 @@
         <v>1831.9</v>
       </c>
       <c r="M58">
-        <v>513.1211792</v>
+        <v>522.2840573999999</v>
       </c>
       <c r="N58">
-        <v>1318.7788208</v>
+        <v>1309.6159426</v>
       </c>
       <c r="O58">
-        <v>395.63364624</v>
+        <v>392.88478278</v>
       </c>
       <c r="P58">
-        <v>923.1451745600002</v>
+        <v>916.7311598200001</v>
       </c>
       <c r="Q58">
-        <v>1323.14517456</v>
+        <v>1316.73115982</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1310787581551353</v>
+        <v>0.132747338508126</v>
       </c>
       <c r="T58">
-        <v>1.240909840163738</v>
+        <v>1.265189717403078</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.57011184542429</v>
+        <v>3.507478304276496</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07914605555849416</v>
+        <v>0.0789398575287288</v>
       </c>
       <c r="C59">
-        <v>11781.94474633617</v>
+        <v>11739.40826155836</v>
       </c>
       <c r="D59">
-        <v>19793.70274633617</v>
+        <v>19916.86026155837</v>
       </c>
       <c r="E59">
-        <v>6936.957999999999</v>
+        <v>7102.652</v>
       </c>
       <c r="F59">
-        <v>9444.557999999999</v>
+        <v>9610.252</v>
       </c>
       <c r="G59">
         <v>1432.8</v>
@@ -6259,28 +6259,28 @@
         <v>1831.9</v>
       </c>
       <c r="M59">
-        <v>522.2840573999999</v>
+        <v>531.4469356000001</v>
       </c>
       <c r="N59">
-        <v>1309.6159426</v>
+        <v>1300.4530644</v>
       </c>
       <c r="O59">
-        <v>392.88478278</v>
+        <v>390.13591932</v>
       </c>
       <c r="P59">
-        <v>916.7311598200001</v>
+        <v>910.31714508</v>
       </c>
       <c r="Q59">
-        <v>1316.73115982</v>
+        <v>1310.31714508</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.132747338508126</v>
+        <v>0.1344953750684019</v>
       </c>
       <c r="T59">
-        <v>1.265189717403078</v>
+        <v>1.290625779272862</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.507478304276496</v>
+        <v>3.447004540409659</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07893985752872881</v>
+        <v>0.07873365949896344</v>
       </c>
       <c r="C60">
-        <v>11739.40826155836</v>
+        <v>11698.4139580854</v>
       </c>
       <c r="D60">
-        <v>19916.86026155835</v>
+        <v>20041.5599580854</v>
       </c>
       <c r="E60">
-        <v>7102.651999999998</v>
+        <v>7268.345999999998</v>
       </c>
       <c r="F60">
-        <v>9610.251999999999</v>
+        <v>9775.945999999998</v>
       </c>
       <c r="G60">
         <v>1432.8</v>
@@ -6341,28 +6341,28 @@
         <v>1831.9</v>
       </c>
       <c r="M60">
-        <v>531.4469356</v>
+        <v>540.6098137999999</v>
       </c>
       <c r="N60">
-        <v>1300.4530644</v>
+        <v>1291.2901862</v>
       </c>
       <c r="O60">
-        <v>390.13591932</v>
+        <v>387.3870558600001</v>
       </c>
       <c r="P60">
-        <v>910.31714508</v>
+        <v>903.9031303400002</v>
       </c>
       <c r="Q60">
-        <v>1310.31714508</v>
+        <v>1303.90313034</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1344953750684019</v>
+        <v>0.1363286817047889</v>
       </c>
       <c r="T60">
-        <v>1.290625779272862</v>
+        <v>1.317302624648489</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.44700454040966</v>
+        <v>3.388580734640005</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07873365949896344</v>
+        <v>0.07852746146919809</v>
       </c>
       <c r="C61">
-        <v>11698.4139580854</v>
+        <v>11658.99098526759</v>
       </c>
       <c r="D61">
-        <v>20041.5599580854</v>
+        <v>20167.83098526759</v>
       </c>
       <c r="E61">
-        <v>7268.345999999998</v>
+        <v>7434.039999999997</v>
       </c>
       <c r="F61">
-        <v>9775.945999999998</v>
+        <v>9941.639999999998</v>
       </c>
       <c r="G61">
         <v>1432.8</v>
@@ -6423,28 +6423,28 @@
         <v>1831.9</v>
       </c>
       <c r="M61">
-        <v>540.6098137999999</v>
+        <v>549.7726919999999</v>
       </c>
       <c r="N61">
-        <v>1291.2901862</v>
+        <v>1282.127308</v>
       </c>
       <c r="O61">
-        <v>387.3870558600001</v>
+        <v>384.6381924</v>
       </c>
       <c r="P61">
-        <v>903.9031303400002</v>
+        <v>897.4891156000001</v>
       </c>
       <c r="Q61">
-        <v>1303.90313034</v>
+        <v>1297.4891156</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1363286817047889</v>
+        <v>0.1382536536729952</v>
       </c>
       <c r="T61">
-        <v>1.317302624648489</v>
+        <v>1.345313312292898</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.388580734640005</v>
+        <v>3.332104389062672</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07852746146919809</v>
+        <v>0.07832126343943274</v>
       </c>
       <c r="C62">
-        <v>11658.99098526759</v>
+        <v>11621.1692317302</v>
       </c>
       <c r="D62">
-        <v>20167.83098526759</v>
+        <v>20295.7032317302</v>
       </c>
       <c r="E62">
-        <v>7434.039999999997</v>
+        <v>7599.733999999999</v>
       </c>
       <c r="F62">
-        <v>9941.639999999998</v>
+        <v>10107.334</v>
       </c>
       <c r="G62">
         <v>1432.8</v>
@@ -6505,28 +6505,28 @@
         <v>1831.9</v>
       </c>
       <c r="M62">
-        <v>549.7726919999999</v>
+        <v>558.9355701999999</v>
       </c>
       <c r="N62">
-        <v>1282.127308</v>
+        <v>1272.9644298</v>
       </c>
       <c r="O62">
-        <v>384.6381924</v>
+        <v>381.8893289400001</v>
       </c>
       <c r="P62">
-        <v>897.4891156000001</v>
+        <v>891.0751008600002</v>
       </c>
       <c r="Q62">
-        <v>1297.4891156</v>
+        <v>1291.07510086</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1382536536729952</v>
+        <v>0.1402773421523916</v>
       </c>
       <c r="T62">
-        <v>1.345313312292898</v>
+        <v>1.374760445457533</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.332104389062672</v>
+        <v>3.27747972694689</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07832126343943274</v>
+        <v>0.07811506540966737</v>
       </c>
       <c r="C63">
-        <v>11621.1692317302</v>
+        <v>11584.97934895948</v>
       </c>
       <c r="D63">
-        <v>20295.7032317302</v>
+        <v>20425.20734895948</v>
       </c>
       <c r="E63">
-        <v>7599.733999999999</v>
+        <v>7765.427999999998</v>
       </c>
       <c r="F63">
-        <v>10107.334</v>
+        <v>10273.028</v>
       </c>
       <c r="G63">
         <v>1432.8</v>
@@ -6587,28 +6587,28 @@
         <v>1831.9</v>
       </c>
       <c r="M63">
-        <v>558.9355701999999</v>
+        <v>568.0984483999999</v>
       </c>
       <c r="N63">
-        <v>1272.9644298</v>
+        <v>1263.8015516</v>
       </c>
       <c r="O63">
-        <v>381.8893289400001</v>
+        <v>379.14046548</v>
       </c>
       <c r="P63">
-        <v>891.0751008600002</v>
+        <v>884.66108612</v>
       </c>
       <c r="Q63">
-        <v>1291.07510086</v>
+        <v>1284.66108612</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1402773421523916</v>
+        <v>0.1424075405517563</v>
       </c>
       <c r="T63">
-        <v>1.374760445457533</v>
+        <v>1.405757427736096</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.27747972694689</v>
+        <v>3.224617150705811</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07811506540966737</v>
+        <v>0.07790886737990202</v>
       </c>
       <c r="C64">
-        <v>11584.97934895948</v>
+        <v>11550.45277579748</v>
       </c>
       <c r="D64">
-        <v>20425.20734895948</v>
+        <v>20556.37477579748</v>
       </c>
       <c r="E64">
-        <v>7765.427999999998</v>
+        <v>7931.121999999998</v>
       </c>
       <c r="F64">
-        <v>10273.028</v>
+        <v>10438.722</v>
       </c>
       <c r="G64">
         <v>1432.8</v>
@@ -6669,28 +6669,28 @@
         <v>1831.9</v>
       </c>
       <c r="M64">
-        <v>568.0984483999999</v>
+        <v>577.2613266</v>
       </c>
       <c r="N64">
-        <v>1263.8015516</v>
+        <v>1254.6386734</v>
       </c>
       <c r="O64">
-        <v>379.14046548</v>
+        <v>376.3916020200001</v>
       </c>
       <c r="P64">
-        <v>884.66108612</v>
+        <v>878.2470713800002</v>
       </c>
       <c r="Q64">
-        <v>1284.66108612</v>
+        <v>1278.24707138</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1424075405517563</v>
+        <v>0.144652884810546</v>
       </c>
       <c r="T64">
-        <v>1.405757427736096</v>
+        <v>1.438429922570258</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.224617150705811</v>
+        <v>3.173432751488259</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07790886737990202</v>
+        <v>0.07770266935013667</v>
       </c>
       <c r="C65">
-        <v>11550.45277579748</v>
+        <v>11517.62176388689</v>
       </c>
       <c r="D65">
-        <v>20556.37477579748</v>
+        <v>20689.23776388689</v>
       </c>
       <c r="E65">
-        <v>7931.121999999998</v>
+        <v>8096.815999999999</v>
       </c>
       <c r="F65">
-        <v>10438.722</v>
+        <v>10604.416</v>
       </c>
       <c r="G65">
         <v>1432.8</v>
@@ -6751,28 +6751,28 @@
         <v>1831.9</v>
       </c>
       <c r="M65">
-        <v>577.2613266</v>
+        <v>586.4242048</v>
       </c>
       <c r="N65">
-        <v>1254.6386734</v>
+        <v>1245.4757952</v>
       </c>
       <c r="O65">
-        <v>376.3916020200001</v>
+        <v>373.64273856</v>
       </c>
       <c r="P65">
-        <v>878.2470713800002</v>
+        <v>871.83305664</v>
       </c>
       <c r="Q65">
-        <v>1278.24707138</v>
+        <v>1271.83305664</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.144652884810546</v>
+        <v>0.1470229704170463</v>
       </c>
       <c r="T65">
-        <v>1.438429922570258</v>
+        <v>1.472917556006317</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.173432751488259</v>
+        <v>3.123847864746254</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07770266935013667</v>
+        <v>0.0774964713203713</v>
       </c>
       <c r="C66">
-        <v>11517.62176388689</v>
+        <v>11486.51940410897</v>
       </c>
       <c r="D66">
-        <v>20689.23776388689</v>
+        <v>20823.82940410896</v>
       </c>
       <c r="E66">
-        <v>8096.815999999999</v>
+        <v>8262.509999999998</v>
       </c>
       <c r="F66">
-        <v>10604.416</v>
+        <v>10770.11</v>
       </c>
       <c r="G66">
         <v>1432.8</v>
@@ -6833,28 +6833,28 @@
         <v>1831.9</v>
       </c>
       <c r="M66">
-        <v>586.4242048</v>
+        <v>595.587083</v>
       </c>
       <c r="N66">
-        <v>1245.4757952</v>
+        <v>1236.312917</v>
       </c>
       <c r="O66">
-        <v>373.64273856</v>
+        <v>370.8938751000001</v>
       </c>
       <c r="P66">
-        <v>871.83305664</v>
+        <v>865.4190419000001</v>
       </c>
       <c r="Q66">
-        <v>1271.83305664</v>
+        <v>1265.4190419</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1470229704170463</v>
+        <v>0.1495284894867751</v>
       </c>
       <c r="T66">
-        <v>1.472917556006317</v>
+        <v>1.509375911353008</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.123847864746254</v>
+        <v>3.075788666827081</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0774964713203713</v>
+        <v>0.07729027329060595</v>
       </c>
       <c r="C67">
-        <v>11486.51940410897</v>
+        <v>11457.17965406011</v>
       </c>
       <c r="D67">
-        <v>20823.82940410896</v>
+        <v>20960.18365406011</v>
       </c>
       <c r="E67">
-        <v>8262.509999999998</v>
+        <v>8428.203999999998</v>
       </c>
       <c r="F67">
-        <v>10770.11</v>
+        <v>10935.804</v>
       </c>
       <c r="G67">
         <v>1432.8</v>
@@ -6915,28 +6915,28 @@
         <v>1831.9</v>
       </c>
       <c r="M67">
-        <v>595.587083</v>
+        <v>604.7499611999999</v>
       </c>
       <c r="N67">
-        <v>1236.312917</v>
+        <v>1227.1500388</v>
       </c>
       <c r="O67">
-        <v>370.8938751000001</v>
+        <v>368.1450116400001</v>
       </c>
       <c r="P67">
-        <v>865.4190419000001</v>
+        <v>859.0050271600001</v>
       </c>
       <c r="Q67">
-        <v>1265.4190419</v>
+        <v>1259.00502716</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1495284894867751</v>
+        <v>0.152181392031194</v>
       </c>
       <c r="T67">
-        <v>1.509375911353008</v>
+        <v>1.54797887583774</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.075788666827081</v>
+        <v>3.029185808238792</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07729027329060595</v>
+        <v>0.07825657526084058</v>
       </c>
       <c r="C68">
-        <v>11457.17965406011</v>
+        <v>10667.45595904066</v>
       </c>
       <c r="D68">
-        <v>20960.18365406011</v>
+        <v>20336.15395904066</v>
       </c>
       <c r="E68">
-        <v>8428.203999999998</v>
+        <v>8593.897999999999</v>
       </c>
       <c r="F68">
-        <v>10935.804</v>
+        <v>11101.498</v>
       </c>
       <c r="G68">
         <v>1432.8</v>
@@ -6997,45 +6997,45 @@
         <v>1831.9</v>
       </c>
       <c r="M68">
-        <v>604.7499611999999</v>
+        <v>641.6665844</v>
       </c>
       <c r="N68">
-        <v>1227.1500388</v>
+        <v>1190.2334156</v>
       </c>
       <c r="O68">
-        <v>368.1450116400001</v>
+        <v>357.07002468</v>
       </c>
       <c r="P68">
-        <v>859.0050271600001</v>
+        <v>833.1633909200002</v>
       </c>
       <c r="Q68">
-        <v>1259.00502716</v>
+        <v>1233.16339092</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.152181392031194</v>
+        <v>0.1549950765480018</v>
       </c>
       <c r="T68">
-        <v>1.54797887583774</v>
+        <v>1.588921413927607</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.029185808238792</v>
+        <v>2.85490945693073</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07825657526084058</v>
+        <v>0.07806787723107522</v>
       </c>
       <c r="C69">
-        <v>10667.45595904066</v>
+        <v>10620.68494110099</v>
       </c>
       <c r="D69">
-        <v>20336.15395904066</v>
+        <v>20455.07694110099</v>
       </c>
       <c r="E69">
-        <v>8593.897999999999</v>
+        <v>8759.591999999999</v>
       </c>
       <c r="F69">
-        <v>11101.498</v>
+        <v>11267.192</v>
       </c>
       <c r="G69">
         <v>1432.8</v>
@@ -7079,28 +7079,28 @@
         <v>1831.9</v>
       </c>
       <c r="M69">
-        <v>641.6665844</v>
+        <v>651.2436976</v>
       </c>
       <c r="N69">
-        <v>1190.2334156</v>
+        <v>1180.6563024</v>
       </c>
       <c r="O69">
-        <v>357.07002468</v>
+        <v>354.1968907200001</v>
       </c>
       <c r="P69">
-        <v>833.1633909200002</v>
+        <v>826.4594116800001</v>
       </c>
       <c r="Q69">
-        <v>1233.16339092</v>
+        <v>1226.45941168</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1549950765480018</v>
+        <v>0.1579846163471101</v>
       </c>
       <c r="T69">
-        <v>1.588921413927607</v>
+        <v>1.63242286064809</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.85490945693073</v>
+        <v>2.812925494328807</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07806787723107522</v>
+        <v>0.07787917920130986</v>
       </c>
       <c r="C70">
-        <v>10620.68494110099</v>
+        <v>10575.31299464427</v>
       </c>
       <c r="D70">
-        <v>20455.07694110099</v>
+        <v>20575.39899464427</v>
       </c>
       <c r="E70">
-        <v>8759.591999999999</v>
+        <v>8925.285999999998</v>
       </c>
       <c r="F70">
-        <v>11267.192</v>
+        <v>11432.886</v>
       </c>
       <c r="G70">
         <v>1432.8</v>
@@ -7161,28 +7161,28 @@
         <v>1831.9</v>
       </c>
       <c r="M70">
-        <v>651.2436976</v>
+        <v>660.8208108</v>
       </c>
       <c r="N70">
-        <v>1180.6563024</v>
+        <v>1171.0791892</v>
       </c>
       <c r="O70">
-        <v>354.1968907200001</v>
+        <v>351.32375676</v>
       </c>
       <c r="P70">
-        <v>826.4594116800001</v>
+        <v>819.7554324400002</v>
       </c>
       <c r="Q70">
-        <v>1226.45941168</v>
+        <v>1219.75543244</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1579846163471101</v>
+        <v>0.1611670296816447</v>
       </c>
       <c r="T70">
-        <v>1.63242286064809</v>
+        <v>1.678730852318283</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.812925494328807</v>
+        <v>2.772158458179114</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07787917920130986</v>
+        <v>0.07769048117154451</v>
       </c>
       <c r="C71">
-        <v>10575.31299464427</v>
+        <v>10531.36495485856</v>
       </c>
       <c r="D71">
-        <v>20575.39899464427</v>
+        <v>20697.14495485856</v>
       </c>
       <c r="E71">
-        <v>8925.285999999998</v>
+        <v>9090.98</v>
       </c>
       <c r="F71">
-        <v>11432.886</v>
+        <v>11598.58</v>
       </c>
       <c r="G71">
         <v>1432.8</v>
@@ -7243,28 +7243,28 @@
         <v>1831.9</v>
       </c>
       <c r="M71">
-        <v>660.8208108</v>
+        <v>670.397924</v>
       </c>
       <c r="N71">
-        <v>1171.0791892</v>
+        <v>1161.502076</v>
       </c>
       <c r="O71">
-        <v>351.32375676</v>
+        <v>348.4506228000001</v>
       </c>
       <c r="P71">
-        <v>819.7554324400002</v>
+        <v>813.0514532000002</v>
       </c>
       <c r="Q71">
-        <v>1219.75543244</v>
+        <v>1213.0514532</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1611670296816447</v>
+        <v>0.1645616039051484</v>
       </c>
       <c r="T71">
-        <v>1.678730852318283</v>
+        <v>1.728126043433154</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.772158458179114</v>
+        <v>2.732556194490841</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07769048117154451</v>
+        <v>0.07750178314177915</v>
       </c>
       <c r="C72">
-        <v>10531.36495485856</v>
+        <v>10488.86624823633</v>
       </c>
       <c r="D72">
-        <v>20697.14495485856</v>
+        <v>20820.34024823633</v>
       </c>
       <c r="E72">
-        <v>9090.98</v>
+        <v>9256.673999999999</v>
       </c>
       <c r="F72">
-        <v>11598.58</v>
+        <v>11764.274</v>
       </c>
       <c r="G72">
         <v>1432.8</v>
@@ -7325,28 +7325,28 @@
         <v>1831.9</v>
       </c>
       <c r="M72">
-        <v>670.397924</v>
+        <v>679.9750372</v>
       </c>
       <c r="N72">
-        <v>1161.502076</v>
+        <v>1151.9249628</v>
       </c>
       <c r="O72">
-        <v>348.4506228000001</v>
+        <v>345.5774888400001</v>
       </c>
       <c r="P72">
-        <v>813.0514532000002</v>
+        <v>806.3474739600001</v>
       </c>
       <c r="Q72">
-        <v>1213.0514532</v>
+        <v>1206.34747396</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1645616039051484</v>
+        <v>0.1681902866957902</v>
       </c>
       <c r="T72">
-        <v>1.728126043433154</v>
+        <v>1.7809277994525</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.732556194490841</v>
+        <v>2.694069487526182</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07750178314177915</v>
+        <v>0.07731308511201379</v>
       </c>
       <c r="C73">
-        <v>10488.86624823633</v>
+        <v>10447.84291027789</v>
       </c>
       <c r="D73">
-        <v>20820.34024823633</v>
+        <v>20945.01091027788</v>
       </c>
       <c r="E73">
-        <v>9256.673999999997</v>
+        <v>9422.367999999997</v>
       </c>
       <c r="F73">
-        <v>11764.274</v>
+        <v>11929.968</v>
       </c>
       <c r="G73">
         <v>1432.8</v>
@@ -7407,28 +7407,28 @@
         <v>1831.9</v>
       </c>
       <c r="M73">
-        <v>679.9750371999999</v>
+        <v>689.5521503999998</v>
       </c>
       <c r="N73">
-        <v>1151.9249628</v>
+        <v>1142.3478496</v>
       </c>
       <c r="O73">
-        <v>345.5774888400001</v>
+        <v>342.70435488</v>
       </c>
       <c r="P73">
-        <v>806.3474739600001</v>
+        <v>799.6434947200003</v>
       </c>
       <c r="Q73">
-        <v>1206.34747396</v>
+        <v>1199.64349472</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1681902866957901</v>
+        <v>0.172078161114335</v>
       </c>
       <c r="T73">
-        <v>1.780927799452499</v>
+        <v>1.837501109473227</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.694069487526182</v>
+        <v>2.656651855754985</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07731308511201379</v>
+        <v>0.07712438708224843</v>
       </c>
       <c r="C74">
-        <v>10447.84291027789</v>
+        <v>10408.32160383469</v>
       </c>
       <c r="D74">
-        <v>20945.01091027788</v>
+        <v>21071.18360383469</v>
       </c>
       <c r="E74">
-        <v>9422.367999999997</v>
+        <v>9588.061999999998</v>
       </c>
       <c r="F74">
-        <v>11929.968</v>
+        <v>12095.662</v>
       </c>
       <c r="G74">
         <v>1432.8</v>
@@ -7489,28 +7489,28 @@
         <v>1831.9</v>
       </c>
       <c r="M74">
-        <v>689.5521503999998</v>
+        <v>699.1292635999999</v>
       </c>
       <c r="N74">
-        <v>1142.3478496</v>
+        <v>1132.7707364</v>
       </c>
       <c r="O74">
-        <v>342.70435488</v>
+        <v>339.8312209200001</v>
       </c>
       <c r="P74">
-        <v>799.6434947200003</v>
+        <v>792.9395154800002</v>
       </c>
       <c r="Q74">
-        <v>1199.64349472</v>
+        <v>1192.93951548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.172078161114335</v>
+        <v>0.1762540262305497</v>
       </c>
       <c r="T74">
-        <v>1.837501109473227</v>
+        <v>1.898265035051045</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.656651855754985</v>
+        <v>2.620259364580259</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07712438708224843</v>
+        <v>0.07693568905248307</v>
       </c>
       <c r="C75">
-        <v>10408.32160383469</v>
+        <v>10370.32963811971</v>
       </c>
       <c r="D75">
-        <v>21071.18360383469</v>
+        <v>21198.88563811971</v>
       </c>
       <c r="E75">
-        <v>9588.061999999998</v>
+        <v>9753.755999999998</v>
       </c>
       <c r="F75">
-        <v>12095.662</v>
+        <v>12261.356</v>
       </c>
       <c r="G75">
         <v>1432.8</v>
@@ -7571,28 +7571,28 @@
         <v>1831.9</v>
       </c>
       <c r="M75">
-        <v>699.1292635999999</v>
+        <v>708.7063767999999</v>
       </c>
       <c r="N75">
-        <v>1132.7707364</v>
+        <v>1123.1936232</v>
       </c>
       <c r="O75">
-        <v>339.8312209200001</v>
+        <v>336.9580869600001</v>
       </c>
       <c r="P75">
-        <v>792.9395154800002</v>
+        <v>786.2355362400002</v>
       </c>
       <c r="Q75">
-        <v>1192.93951548</v>
+        <v>1186.23553624</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1762540262305497</v>
+        <v>0.1807511117403195</v>
       </c>
       <c r="T75">
-        <v>1.898265035051045</v>
+        <v>1.963703108750234</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.620259364580259</v>
+        <v>2.584850454248093</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07693568905248307</v>
+        <v>0.0767469910227177</v>
       </c>
       <c r="C76">
-        <v>10370.32963811971</v>
+        <v>10333.89498841318</v>
       </c>
       <c r="D76">
-        <v>21198.88563811971</v>
+        <v>21328.14498841318</v>
       </c>
       <c r="E76">
-        <v>9753.755999999998</v>
+        <v>9919.449999999999</v>
       </c>
       <c r="F76">
-        <v>12261.356</v>
+        <v>12427.05</v>
       </c>
       <c r="G76">
         <v>1432.8</v>
@@ -7653,28 +7653,28 @@
         <v>1831.9</v>
       </c>
       <c r="M76">
-        <v>708.7063767999999</v>
+        <v>718.28349</v>
       </c>
       <c r="N76">
-        <v>1123.1936232</v>
+        <v>1113.61651</v>
       </c>
       <c r="O76">
-        <v>336.9580869600001</v>
+        <v>334.084953</v>
       </c>
       <c r="P76">
-        <v>786.2355362400002</v>
+        <v>779.531557</v>
       </c>
       <c r="Q76">
-        <v>1186.23553624</v>
+        <v>1179.531557</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1807511117403195</v>
+        <v>0.1856079640908708</v>
       </c>
       <c r="T76">
-        <v>1.963703108750234</v>
+        <v>2.034376228345358</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.584850454248093</v>
+        <v>2.550385781524785</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0767469910227177</v>
+        <v>0.07655829299295236</v>
       </c>
       <c r="C77">
-        <v>10333.89498841318</v>
+        <v>10299.04631649382</v>
       </c>
       <c r="D77">
-        <v>21328.14498841318</v>
+        <v>21458.99031649382</v>
       </c>
       <c r="E77">
-        <v>9919.449999999999</v>
+        <v>10085.144</v>
       </c>
       <c r="F77">
-        <v>12427.05</v>
+        <v>12592.744</v>
       </c>
       <c r="G77">
         <v>1432.8</v>
@@ -7735,28 +7735,28 @@
         <v>1831.9</v>
       </c>
       <c r="M77">
-        <v>718.28349</v>
+        <v>727.8606032</v>
       </c>
       <c r="N77">
-        <v>1113.61651</v>
+        <v>1104.0393968</v>
       </c>
       <c r="O77">
-        <v>334.084953</v>
+        <v>331.21181904</v>
       </c>
       <c r="P77">
-        <v>779.531557</v>
+        <v>772.8275777600001</v>
       </c>
       <c r="Q77">
-        <v>1179.531557</v>
+        <v>1172.82757776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1856079640908708</v>
+        <v>0.1908695541373015</v>
       </c>
       <c r="T77">
-        <v>2.034376228345358</v>
+        <v>2.11093877457341</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.550385781524785</v>
+        <v>2.516828073873143</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07655829299295236</v>
+        <v>0.078256094963187</v>
       </c>
       <c r="C78">
-        <v>10299.04631649382</v>
+        <v>9010.816901191603</v>
       </c>
       <c r="D78">
-        <v>21458.99031649382</v>
+        <v>20336.4549011916</v>
       </c>
       <c r="E78">
-        <v>10085.144</v>
+        <v>10250.838</v>
       </c>
       <c r="F78">
-        <v>12592.744</v>
+        <v>12758.438</v>
       </c>
       <c r="G78">
         <v>1432.8</v>
@@ -7817,45 +7817,45 @@
         <v>1831.9</v>
       </c>
       <c r="M78">
-        <v>727.8606032</v>
+        <v>782.0922493999999</v>
       </c>
       <c r="N78">
-        <v>1104.0393968</v>
+        <v>1049.8077506</v>
       </c>
       <c r="O78">
-        <v>331.21181904</v>
+        <v>314.9423251800001</v>
       </c>
       <c r="P78">
-        <v>772.8275777600001</v>
+        <v>734.8654254200001</v>
       </c>
       <c r="Q78">
-        <v>1172.82757776</v>
+        <v>1134.86542542</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1908695541373015</v>
+        <v>0.1965886737529869</v>
       </c>
       <c r="T78">
-        <v>2.11093877457341</v>
+        <v>2.194158933516944</v>
       </c>
       <c r="U78">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.516828073873143</v>
+        <v>2.342306807675673</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.078256094963187</v>
+        <v>0.07809189693342164</v>
       </c>
       <c r="C79">
-        <v>9010.816901191603</v>
+        <v>8948.529828139015</v>
       </c>
       <c r="D79">
-        <v>20336.4549011916</v>
+        <v>20439.86182813902</v>
       </c>
       <c r="E79">
-        <v>10250.838</v>
+        <v>10416.532</v>
       </c>
       <c r="F79">
-        <v>12758.438</v>
+        <v>12924.132</v>
       </c>
       <c r="G79">
         <v>1432.8</v>
@@ -7899,28 +7899,28 @@
         <v>1831.9</v>
       </c>
       <c r="M79">
-        <v>782.0922493999999</v>
+        <v>792.2492916</v>
       </c>
       <c r="N79">
-        <v>1049.8077506</v>
+        <v>1039.6507084</v>
       </c>
       <c r="O79">
-        <v>314.9423251800001</v>
+        <v>311.89521252</v>
       </c>
       <c r="P79">
-        <v>734.8654254200001</v>
+        <v>727.75549588</v>
       </c>
       <c r="Q79">
-        <v>1134.86542542</v>
+        <v>1127.75549588</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1965886737529869</v>
+        <v>0.2028277133337347</v>
       </c>
       <c r="T79">
-        <v>2.194158933516944</v>
+        <v>2.284944561455344</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.342306807675673</v>
+        <v>2.312277233218292</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07809189693342164</v>
+        <v>0.07792769890365628</v>
       </c>
       <c r="C80">
-        <v>8948.529828139015</v>
+        <v>8887.299737954692</v>
       </c>
       <c r="D80">
-        <v>20439.86182813902</v>
+        <v>20544.32573795469</v>
       </c>
       <c r="E80">
-        <v>10416.532</v>
+        <v>10582.226</v>
       </c>
       <c r="F80">
-        <v>12924.132</v>
+        <v>13089.826</v>
       </c>
       <c r="G80">
         <v>1432.8</v>
@@ -7981,28 +7981,28 @@
         <v>1831.9</v>
       </c>
       <c r="M80">
-        <v>792.2492916</v>
+        <v>802.4063338</v>
       </c>
       <c r="N80">
-        <v>1039.6507084</v>
+        <v>1029.4936662</v>
       </c>
       <c r="O80">
-        <v>311.89521252</v>
+        <v>308.84809986</v>
       </c>
       <c r="P80">
-        <v>727.75549588</v>
+        <v>720.64556634</v>
       </c>
       <c r="Q80">
-        <v>1127.75549588</v>
+        <v>1120.64556634</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2028277133337347</v>
+        <v>0.209660947160268</v>
       </c>
       <c r="T80">
-        <v>2.284944561455344</v>
+        <v>2.384376439673593</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.312277233218292</v>
+        <v>2.283007901152238</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07792769890365628</v>
+        <v>0.07776350087389092</v>
       </c>
       <c r="C81">
-        <v>8887.299737954692</v>
+        <v>8827.142919952968</v>
       </c>
       <c r="D81">
-        <v>20544.32573795469</v>
+        <v>20649.86291995297</v>
       </c>
       <c r="E81">
-        <v>10582.226</v>
+        <v>10747.92</v>
       </c>
       <c r="F81">
-        <v>13089.826</v>
+        <v>13255.52</v>
       </c>
       <c r="G81">
         <v>1432.8</v>
@@ -8063,28 +8063,28 @@
         <v>1831.9</v>
       </c>
       <c r="M81">
-        <v>802.4063338</v>
+        <v>812.5633759999999</v>
       </c>
       <c r="N81">
-        <v>1029.4936662</v>
+        <v>1019.336624</v>
       </c>
       <c r="O81">
-        <v>308.84809986</v>
+        <v>305.8009872</v>
       </c>
       <c r="P81">
-        <v>720.64556634</v>
+        <v>713.5356368000001</v>
       </c>
       <c r="Q81">
-        <v>1120.64556634</v>
+        <v>1113.5356368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.209660947160268</v>
+        <v>0.2171775043694546</v>
       </c>
       <c r="T81">
-        <v>2.384376439673593</v>
+        <v>2.493751505713666</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.283007901152238</v>
+        <v>2.254470302387835</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07776350087389092</v>
+        <v>0.07918690284412555</v>
       </c>
       <c r="C82">
-        <v>8827.142919952968</v>
+        <v>7781.072093669787</v>
       </c>
       <c r="D82">
-        <v>20649.86291995297</v>
+        <v>19769.48609366979</v>
       </c>
       <c r="E82">
-        <v>10747.92</v>
+        <v>10913.614</v>
       </c>
       <c r="F82">
-        <v>13255.52</v>
+        <v>13421.214</v>
       </c>
       <c r="G82">
         <v>1432.8</v>
@@ -8145,45 +8145,45 @@
         <v>1831.9</v>
       </c>
       <c r="M82">
-        <v>812.5633759999999</v>
+        <v>860.2998174000001</v>
       </c>
       <c r="N82">
-        <v>1019.336624</v>
+        <v>971.6001826</v>
       </c>
       <c r="O82">
-        <v>305.8009872</v>
+        <v>291.48005478</v>
       </c>
       <c r="P82">
-        <v>713.5356368000001</v>
+        <v>680.1201278200001</v>
       </c>
       <c r="Q82">
-        <v>1113.5356368</v>
+        <v>1080.12012782</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2171775043694546</v>
+        <v>0.2254852781269766</v>
       </c>
       <c r="T82">
-        <v>2.493751505713666</v>
+        <v>2.614639736600062</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.254470302387835</v>
+        <v>2.129373926332302</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07918690284412555</v>
+        <v>0.0790423048143602</v>
       </c>
       <c r="C83">
-        <v>7781.072093669787</v>
+        <v>7701.371792198879</v>
       </c>
       <c r="D83">
-        <v>19769.48609366979</v>
+        <v>19855.47979219888</v>
       </c>
       <c r="E83">
-        <v>10913.614</v>
+        <v>11079.308</v>
       </c>
       <c r="F83">
-        <v>13421.214</v>
+        <v>13586.908</v>
       </c>
       <c r="G83">
         <v>1432.8</v>
@@ -8227,28 +8227,28 @@
         <v>1831.9</v>
       </c>
       <c r="M83">
-        <v>860.2998174000001</v>
+        <v>870.9208028</v>
       </c>
       <c r="N83">
-        <v>971.6001826</v>
+        <v>960.9791972</v>
       </c>
       <c r="O83">
-        <v>291.48005478</v>
+        <v>288.29375916</v>
       </c>
       <c r="P83">
-        <v>680.1201278200001</v>
+        <v>672.68543804</v>
       </c>
       <c r="Q83">
-        <v>1080.12012782</v>
+        <v>1072.68543804</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2254852781269766</v>
+        <v>0.2347161378575567</v>
       </c>
       <c r="T83">
-        <v>2.614639736600062</v>
+        <v>2.748959993140503</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.129373926332302</v>
+        <v>2.103405951620932</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0790423048143602</v>
+        <v>0.07889770678459482</v>
       </c>
       <c r="C84">
-        <v>7701.371792198879</v>
+        <v>7622.422873260944</v>
       </c>
       <c r="D84">
-        <v>19855.47979219888</v>
+        <v>19942.22487326094</v>
       </c>
       <c r="E84">
-        <v>11079.308</v>
+        <v>11245.002</v>
       </c>
       <c r="F84">
-        <v>13586.908</v>
+        <v>13752.602</v>
       </c>
       <c r="G84">
         <v>1432.8</v>
@@ -8309,28 +8309,28 @@
         <v>1831.9</v>
       </c>
       <c r="M84">
-        <v>870.9208028</v>
+        <v>881.5417882</v>
       </c>
       <c r="N84">
-        <v>960.9791972</v>
+        <v>950.3582118</v>
       </c>
       <c r="O84">
-        <v>288.29375916</v>
+        <v>285.10746354</v>
       </c>
       <c r="P84">
-        <v>672.68543804</v>
+        <v>665.25074826</v>
       </c>
       <c r="Q84">
-        <v>1072.68543804</v>
+        <v>1065.25074826</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2347161378575567</v>
+        <v>0.245032981085852</v>
       </c>
       <c r="T84">
-        <v>2.748959993140503</v>
+        <v>2.899082632803348</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.103405951620932</v>
+        <v>2.078063711239957</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07889770678459482</v>
+        <v>0.07875310875482949</v>
       </c>
       <c r="C85">
-        <v>7622.422873260944</v>
+        <v>7544.235228041145</v>
       </c>
       <c r="D85">
-        <v>19942.22487326094</v>
+        <v>20029.73122804115</v>
       </c>
       <c r="E85">
-        <v>11245.002</v>
+        <v>11410.696</v>
       </c>
       <c r="F85">
-        <v>13752.602</v>
+        <v>13918.296</v>
       </c>
       <c r="G85">
         <v>1432.8</v>
@@ -8391,28 +8391,28 @@
         <v>1831.9</v>
       </c>
       <c r="M85">
-        <v>881.5417882</v>
+        <v>892.1627736</v>
       </c>
       <c r="N85">
-        <v>950.3582118</v>
+        <v>939.7372264000001</v>
       </c>
       <c r="O85">
-        <v>285.10746354</v>
+        <v>281.92116792</v>
       </c>
       <c r="P85">
-        <v>665.25074826</v>
+        <v>657.81605848</v>
       </c>
       <c r="Q85">
-        <v>1065.25074826</v>
+        <v>1057.81605848</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.245032981085852</v>
+        <v>0.2566394297176844</v>
       </c>
       <c r="T85">
-        <v>2.899082632803348</v>
+        <v>3.067970602424051</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.078063711239957</v>
+        <v>2.05332485753472</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07875310875482947</v>
+        <v>0.07860851072506411</v>
       </c>
       <c r="C86">
-        <v>7544.235228041165</v>
+        <v>7466.818922099726</v>
       </c>
       <c r="D86">
-        <v>20029.73122804116</v>
+        <v>20118.00892209973</v>
       </c>
       <c r="E86">
-        <v>11410.696</v>
+        <v>11576.39</v>
       </c>
       <c r="F86">
-        <v>13918.296</v>
+        <v>14083.99</v>
       </c>
       <c r="G86">
         <v>1432.8</v>
@@ -8473,28 +8473,28 @@
         <v>1831.9</v>
       </c>
       <c r="M86">
-        <v>892.1627735999999</v>
+        <v>902.7837589999999</v>
       </c>
       <c r="N86">
-        <v>939.7372264000002</v>
+        <v>929.1162410000002</v>
       </c>
       <c r="O86">
-        <v>281.92116792</v>
+        <v>278.7348723000001</v>
       </c>
       <c r="P86">
-        <v>657.8160584800002</v>
+        <v>650.3813687000002</v>
       </c>
       <c r="Q86">
-        <v>1057.81605848</v>
+        <v>1050.3813687</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2566394297176842</v>
+        <v>0.2697934048337607</v>
       </c>
       <c r="T86">
-        <v>3.067970602424048</v>
+        <v>3.259376967994176</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.05332485753472</v>
+        <v>2.029168094504899</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07860851072506411</v>
+        <v>0.07846391269529876</v>
       </c>
       <c r="C87">
-        <v>7466.818922099726</v>
+        <v>7390.184199231462</v>
       </c>
       <c r="D87">
-        <v>20118.00892209973</v>
+        <v>20207.06819923146</v>
       </c>
       <c r="E87">
-        <v>11576.39</v>
+        <v>11742.084</v>
       </c>
       <c r="F87">
-        <v>14083.99</v>
+        <v>14249.684</v>
       </c>
       <c r="G87">
         <v>1432.8</v>
@@ -8555,28 +8555,28 @@
         <v>1831.9</v>
       </c>
       <c r="M87">
-        <v>902.7837589999999</v>
+        <v>913.4047443999999</v>
       </c>
       <c r="N87">
-        <v>929.1162410000002</v>
+        <v>918.4952556000002</v>
       </c>
       <c r="O87">
-        <v>278.7348723000001</v>
+        <v>275.5485766800001</v>
       </c>
       <c r="P87">
-        <v>650.3813687000002</v>
+        <v>642.9466789200001</v>
       </c>
       <c r="Q87">
-        <v>1050.3813687</v>
+        <v>1042.94667892</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2697934048337607</v>
+        <v>0.284826519252134</v>
       </c>
       <c r="T87">
-        <v>3.259376967994176</v>
+        <v>3.478127100074322</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.029168094504899</v>
+        <v>2.005573116661819</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07846391269529876</v>
+        <v>0.0830695146655334</v>
       </c>
       <c r="C88">
-        <v>7390.184199231462</v>
+        <v>4727.389983512452</v>
       </c>
       <c r="D88">
-        <v>20207.06819923146</v>
+        <v>17709.96798351245</v>
       </c>
       <c r="E88">
-        <v>11742.084</v>
+        <v>11907.778</v>
       </c>
       <c r="F88">
-        <v>14249.684</v>
+        <v>14415.378</v>
       </c>
       <c r="G88">
         <v>1432.8</v>
@@ -8637,45 +8637,45 @@
         <v>1831.9</v>
       </c>
       <c r="M88">
-        <v>913.4047443999999</v>
+        <v>1036.4656782</v>
       </c>
       <c r="N88">
-        <v>918.4952556000002</v>
+        <v>795.4343218000001</v>
       </c>
       <c r="O88">
-        <v>275.5485766800001</v>
+        <v>238.63029654</v>
       </c>
       <c r="P88">
-        <v>642.9466789200001</v>
+        <v>556.8040252600001</v>
       </c>
       <c r="Q88">
-        <v>1042.94667892</v>
+        <v>956.8040252600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.284826519252134</v>
+        <v>0.3021724205041031</v>
       </c>
       <c r="T88">
-        <v>3.478127100074322</v>
+        <v>3.730531098628337</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.3</v>
       </c>
       <c r="W88">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.005573116661819</v>
+        <v>1.76744878149888</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0830695146655334</v>
+        <v>0.08538191663576805</v>
       </c>
       <c r="C89">
-        <v>4727.389983512452</v>
+        <v>3527.067841709433</v>
       </c>
       <c r="D89">
-        <v>17709.96798351245</v>
+        <v>16675.33984170943</v>
       </c>
       <c r="E89">
-        <v>11907.778</v>
+        <v>12073.472</v>
       </c>
       <c r="F89">
-        <v>14415.378</v>
+        <v>14581.072</v>
       </c>
       <c r="G89">
         <v>1432.8</v>
@@ -8719,45 +8719,45 @@
         <v>1831.9</v>
       </c>
       <c r="M89">
-        <v>1036.4656782</v>
+        <v>1105.2452576</v>
       </c>
       <c r="N89">
-        <v>795.4343218000001</v>
+        <v>726.6547424</v>
       </c>
       <c r="O89">
-        <v>238.63029654</v>
+        <v>217.99642272</v>
       </c>
       <c r="P89">
-        <v>556.8040252600001</v>
+        <v>508.65831968</v>
       </c>
       <c r="Q89">
-        <v>956.8040252600001</v>
+        <v>908.65831968</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3021724205041031</v>
+        <v>0.3224093052980671</v>
       </c>
       <c r="T89">
-        <v>3.730531098628337</v>
+        <v>4.025002430274689</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.3</v>
       </c>
       <c r="W89">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.76744878149888</v>
+        <v>1.657460176737518</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08538191663576805</v>
+        <v>0.08531921860600269</v>
       </c>
       <c r="C90">
-        <v>3527.067841709433</v>
+        <v>3387.829601479547</v>
       </c>
       <c r="D90">
-        <v>16675.33984170943</v>
+        <v>16701.79560147955</v>
       </c>
       <c r="E90">
-        <v>12073.472</v>
+        <v>12239.166</v>
       </c>
       <c r="F90">
-        <v>14581.072</v>
+        <v>14746.766</v>
       </c>
       <c r="G90">
         <v>1432.8</v>
@@ -8801,28 +8801,28 @@
         <v>1831.9</v>
       </c>
       <c r="M90">
-        <v>1105.2452576</v>
+        <v>1117.8048628</v>
       </c>
       <c r="N90">
-        <v>726.6547424</v>
+        <v>714.0951372000002</v>
       </c>
       <c r="O90">
-        <v>217.99642272</v>
+        <v>214.22854116</v>
       </c>
       <c r="P90">
-        <v>508.65831968</v>
+        <v>499.8665960400001</v>
       </c>
       <c r="Q90">
-        <v>908.65831968</v>
+        <v>899.8665960400001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3224093052980671</v>
+        <v>0.3463256236909335</v>
       </c>
       <c r="T90">
-        <v>4.025002430274689</v>
+        <v>4.373014004038557</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.657460176737518</v>
+        <v>1.638837028684288</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08531921860600269</v>
+        <v>0.08525652057623732</v>
       </c>
       <c r="C91">
-        <v>3387.829601479547</v>
+        <v>3248.675439824729</v>
       </c>
       <c r="D91">
-        <v>16701.79560147955</v>
+        <v>16728.33543982473</v>
       </c>
       <c r="E91">
-        <v>12239.166</v>
+        <v>12404.86</v>
       </c>
       <c r="F91">
-        <v>14746.766</v>
+        <v>14912.46</v>
       </c>
       <c r="G91">
         <v>1432.8</v>
@@ -8883,28 +8883,28 @@
         <v>1831.9</v>
       </c>
       <c r="M91">
-        <v>1117.8048628</v>
+        <v>1130.364468</v>
       </c>
       <c r="N91">
-        <v>714.0951372000002</v>
+        <v>701.5355320000001</v>
       </c>
       <c r="O91">
-        <v>214.22854116</v>
+        <v>210.4606596</v>
       </c>
       <c r="P91">
-        <v>499.8665960400001</v>
+        <v>491.0748724000001</v>
       </c>
       <c r="Q91">
-        <v>899.8665960400001</v>
+        <v>891.0748724000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3463256236909335</v>
+        <v>0.3750252057623733</v>
       </c>
       <c r="T91">
-        <v>4.373014004038557</v>
+        <v>4.790627892555199</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.638837028684288</v>
+        <v>1.620627728365573</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08525652057623732</v>
+        <v>0.08519382254647197</v>
       </c>
       <c r="C92">
-        <v>3248.675439824729</v>
+        <v>3109.605758195805</v>
       </c>
       <c r="D92">
-        <v>16728.33543982473</v>
+        <v>16754.9597581958</v>
       </c>
       <c r="E92">
-        <v>12404.86</v>
+        <v>12570.554</v>
       </c>
       <c r="F92">
-        <v>14912.46</v>
+        <v>15078.154</v>
       </c>
       <c r="G92">
         <v>1432.8</v>
@@ -8965,28 +8965,28 @@
         <v>1831.9</v>
       </c>
       <c r="M92">
-        <v>1130.364468</v>
+        <v>1142.9240732</v>
       </c>
       <c r="N92">
-        <v>701.5355320000001</v>
+        <v>688.9759268</v>
       </c>
       <c r="O92">
-        <v>210.4606596</v>
+        <v>206.69277804</v>
       </c>
       <c r="P92">
-        <v>491.0748724000001</v>
+        <v>482.28314876</v>
       </c>
       <c r="Q92">
-        <v>891.0748724000001</v>
+        <v>882.28314876</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3750252057623733</v>
+        <v>0.4101024727385775</v>
       </c>
       <c r="T92">
-        <v>4.790627892555199</v>
+        <v>5.301044867408875</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.620627728365573</v>
+        <v>1.602818632449468</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08519382254647197</v>
+        <v>0.08513112451670661</v>
       </c>
       <c r="C93">
-        <v>3109.605758195805</v>
+        <v>2970.620960603443</v>
       </c>
       <c r="D93">
-        <v>16754.9597581958</v>
+        <v>16781.66896060344</v>
       </c>
       <c r="E93">
-        <v>12570.554</v>
+        <v>12736.248</v>
       </c>
       <c r="F93">
-        <v>15078.154</v>
+        <v>15243.848</v>
       </c>
       <c r="G93">
         <v>1432.8</v>
@@ -9047,28 +9047,28 @@
         <v>1831.9</v>
       </c>
       <c r="M93">
-        <v>1142.9240732</v>
+        <v>1155.4836784</v>
       </c>
       <c r="N93">
-        <v>688.9759268</v>
+        <v>676.4163216000002</v>
       </c>
       <c r="O93">
-        <v>206.69277804</v>
+        <v>202.9248964800001</v>
       </c>
       <c r="P93">
-        <v>482.28314876</v>
+        <v>473.4914251200001</v>
       </c>
       <c r="Q93">
-        <v>882.28314876</v>
+        <v>873.4914251200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4101024727385775</v>
+        <v>0.4539490564588328</v>
       </c>
       <c r="T93">
-        <v>5.301044867408875</v>
+        <v>5.939066085975969</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.602818632449468</v>
+        <v>1.585396690792409</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08513112451670661</v>
+        <v>0.08506842648694124</v>
       </c>
       <c r="C94">
-        <v>2970.620960603443</v>
+        <v>2831.721453638564</v>
       </c>
       <c r="D94">
-        <v>16781.66896060344</v>
+        <v>16808.46345363856</v>
       </c>
       <c r="E94">
-        <v>12736.248</v>
+        <v>12901.942</v>
       </c>
       <c r="F94">
-        <v>15243.848</v>
+        <v>15409.542</v>
       </c>
       <c r="G94">
         <v>1432.8</v>
@@ -9129,28 +9129,28 @@
         <v>1831.9</v>
       </c>
       <c r="M94">
-        <v>1155.4836784</v>
+        <v>1168.0432836</v>
       </c>
       <c r="N94">
-        <v>676.4163216000002</v>
+        <v>663.8567164000001</v>
       </c>
       <c r="O94">
-        <v>202.9248964800001</v>
+        <v>199.15701492</v>
       </c>
       <c r="P94">
-        <v>473.4914251200001</v>
+        <v>464.69970148</v>
       </c>
       <c r="Q94">
-        <v>873.4914251200001</v>
+        <v>864.69970148</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4539490564588328</v>
+        <v>0.5103232355277324</v>
       </c>
       <c r="T94">
-        <v>5.939066085975969</v>
+        <v>6.759379081276518</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.585396690792409</v>
+        <v>1.568349414547329</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08506842648694124</v>
+        <v>0.08500572845717588</v>
       </c>
       <c r="C95">
-        <v>2831.721453638564</v>
+        <v>2692.907646492962</v>
       </c>
       <c r="D95">
-        <v>16808.46345363856</v>
+        <v>16835.34364649296</v>
       </c>
       <c r="E95">
-        <v>12901.942</v>
+        <v>13067.636</v>
       </c>
       <c r="F95">
-        <v>15409.542</v>
+        <v>15575.236</v>
       </c>
       <c r="G95">
         <v>1432.8</v>
@@ -9211,28 +9211,28 @@
         <v>1831.9</v>
       </c>
       <c r="M95">
-        <v>1168.0432836</v>
+        <v>1180.6028888</v>
       </c>
       <c r="N95">
-        <v>663.8567164000001</v>
+        <v>651.2971112</v>
       </c>
       <c r="O95">
-        <v>199.15701492</v>
+        <v>195.38913336</v>
       </c>
       <c r="P95">
-        <v>464.69970148</v>
+        <v>455.9079778400001</v>
       </c>
       <c r="Q95">
-        <v>864.69970148</v>
+        <v>855.9079778400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5103232355277324</v>
+        <v>0.5854888076195987</v>
       </c>
       <c r="T95">
-        <v>6.759379081276518</v>
+        <v>7.853129741677251</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.568349414547329</v>
+        <v>1.551664846307464</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08500572845717588</v>
+        <v>0.08494303042741053</v>
       </c>
       <c r="C96">
-        <v>2692.907646492962</v>
+        <v>2554.179950980177</v>
       </c>
       <c r="D96">
-        <v>16835.34364649296</v>
+        <v>16862.30995098018</v>
       </c>
       <c r="E96">
-        <v>13067.636</v>
+        <v>13233.33</v>
       </c>
       <c r="F96">
-        <v>15575.236</v>
+        <v>15740.93</v>
       </c>
       <c r="G96">
         <v>1432.8</v>
@@ -9293,28 +9293,28 @@
         <v>1831.9</v>
       </c>
       <c r="M96">
-        <v>1180.6028888</v>
+        <v>1193.162494</v>
       </c>
       <c r="N96">
-        <v>651.2971112</v>
+        <v>638.7375060000002</v>
       </c>
       <c r="O96">
-        <v>195.38913336</v>
+        <v>191.6212518</v>
       </c>
       <c r="P96">
-        <v>455.9079778400001</v>
+        <v>447.1162542000001</v>
       </c>
       <c r="Q96">
-        <v>855.9079778400001</v>
+        <v>847.1162542000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5854888076195987</v>
+        <v>0.6907206085482114</v>
       </c>
       <c r="T96">
-        <v>7.853129741677251</v>
+        <v>9.384380666238279</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.551664846307464</v>
+        <v>1.535331532135807</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08494303042741053</v>
+        <v>0.08488033239764517</v>
       </c>
       <c r="C97">
-        <v>2554.179950980177</v>
+        <v>2415.538781556483</v>
       </c>
       <c r="D97">
-        <v>16862.30995098018</v>
+        <v>16889.36278155648</v>
       </c>
       <c r="E97">
-        <v>13233.33</v>
+        <v>13399.024</v>
       </c>
       <c r="F97">
-        <v>15740.93</v>
+        <v>15906.624</v>
       </c>
       <c r="G97">
         <v>1432.8</v>
@@ -9375,28 +9375,28 @@
         <v>1831.9</v>
       </c>
       <c r="M97">
-        <v>1193.162494</v>
+        <v>1205.7220992</v>
       </c>
       <c r="N97">
-        <v>638.7375060000002</v>
+        <v>626.1779008000001</v>
       </c>
       <c r="O97">
-        <v>191.6212518</v>
+        <v>187.85337024</v>
       </c>
       <c r="P97">
-        <v>447.1162542000001</v>
+        <v>438.3245305600001</v>
       </c>
       <c r="Q97">
-        <v>847.1162542000002</v>
+        <v>838.3245305600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6907206085482114</v>
+        <v>0.8485683099411307</v>
       </c>
       <c r="T97">
-        <v>9.384380666238279</v>
+        <v>11.68125705307982</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.535331532135807</v>
+        <v>1.519338495342725</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08488033239764517</v>
+        <v>0.08481763436787983</v>
       </c>
       <c r="C98">
-        <v>2415.538781556485</v>
+        <v>2276.984555342142</v>
       </c>
       <c r="D98">
-        <v>16889.36278155648</v>
+        <v>16916.50255534214</v>
       </c>
       <c r="E98">
-        <v>13399.024</v>
+        <v>13564.718</v>
       </c>
       <c r="F98">
-        <v>15906.624</v>
+        <v>16072.318</v>
       </c>
       <c r="G98">
         <v>1432.8</v>
@@ -9457,28 +9457,28 @@
         <v>1831.9</v>
       </c>
       <c r="M98">
-        <v>1205.7220992</v>
+        <v>1218.2817044</v>
       </c>
       <c r="N98">
-        <v>626.1779008000001</v>
+        <v>613.6182956000002</v>
       </c>
       <c r="O98">
-        <v>187.85337024</v>
+        <v>184.0854886800001</v>
       </c>
       <c r="P98">
-        <v>438.3245305600001</v>
+        <v>429.5328069200002</v>
       </c>
       <c r="Q98">
-        <v>838.3245305600001</v>
+        <v>829.5328069200002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8485683099411285</v>
+        <v>1.11164781226266</v>
       </c>
       <c r="T98">
-        <v>11.68125705307979</v>
+        <v>15.50938436448235</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.519338495342725</v>
+        <v>1.503675211885584</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08481763436787983</v>
+        <v>0.09449613633811446</v>
       </c>
       <c r="C99">
-        <v>2276.984555342142</v>
+        <v>-1250.914654831986</v>
       </c>
       <c r="D99">
-        <v>16916.50255534214</v>
+        <v>13554.29734516801</v>
       </c>
       <c r="E99">
-        <v>13564.718</v>
+        <v>13730.412</v>
       </c>
       <c r="F99">
-        <v>16072.318</v>
+        <v>16238.012</v>
       </c>
       <c r="G99">
         <v>1432.8</v>
@@ -9539,45 +9539,45 @@
         <v>1831.9</v>
       </c>
       <c r="M99">
-        <v>1218.2817044</v>
+        <v>1461.42108</v>
       </c>
       <c r="N99">
-        <v>613.6182956000002</v>
+        <v>370.4789200000005</v>
       </c>
       <c r="O99">
-        <v>184.0854886800001</v>
+        <v>111.1436760000001</v>
       </c>
       <c r="P99">
-        <v>429.5328069200002</v>
+        <v>259.3352440000003</v>
       </c>
       <c r="Q99">
-        <v>829.5328069200002</v>
+        <v>659.3352440000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.11164781226266</v>
+        <v>1.637806816905721</v>
       </c>
       <c r="T99">
-        <v>15.50938436448235</v>
+        <v>23.16563898728745</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.3</v>
       </c>
       <c r="W99">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.503675211885584</v>
+        <v>1.253505936837862</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09449613633811446</v>
+        <v>0.1171910591938731</v>
       </c>
       <c r="C100">
-        <v>-1250.914654831986</v>
+        <v>-5725.463798404387</v>
       </c>
       <c r="D100">
-        <v>13554.29734516801</v>
+        <v>9245.442201595612</v>
       </c>
       <c r="E100">
-        <v>13730.412</v>
+        <v>13896.106</v>
       </c>
       <c r="F100">
-        <v>16238.012</v>
+        <v>16403.706</v>
       </c>
       <c r="G100">
         <v>1432.8</v>
@@ -9621,129 +9621,47 @@
         <v>1831.9</v>
       </c>
       <c r="M100">
-        <v>1461.42108</v>
+        <v>1945.4795316</v>
       </c>
       <c r="N100">
-        <v>370.4789200000005</v>
+        <v>-113.5795315999999</v>
       </c>
       <c r="O100">
-        <v>111.1436760000001</v>
+        <v>-34.07385947999996</v>
       </c>
       <c r="P100">
-        <v>259.3352440000003</v>
+        <v>-79.50567211999993</v>
       </c>
       <c r="Q100">
-        <v>659.3352440000003</v>
+        <v>320.4943278800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.637806816905721</v>
+        <v>3.294482628260285</v>
       </c>
       <c r="T100">
-        <v>23.16563898728745</v>
+        <v>47.27229064057877</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.3</v>
+        <v>0.2824856242758941</v>
       </c>
       <c r="W100">
-        <v>0.063</v>
+        <v>0.08509720496087897</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.253505936837862</v>
+        <v>0.9416187475863137</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1171910591938731</v>
-      </c>
-      <c r="C101">
-        <v>-5725.463798404387</v>
-      </c>
-      <c r="D101">
-        <v>9245.442201595612</v>
-      </c>
-      <c r="E101">
-        <v>13896.106</v>
-      </c>
-      <c r="F101">
-        <v>16403.706</v>
-      </c>
-      <c r="G101">
-        <v>1432.8</v>
-      </c>
-      <c r="H101">
-        <v>14061.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2231.9</v>
-      </c>
-      <c r="K101">
-        <v>400</v>
-      </c>
-      <c r="L101">
-        <v>1831.9</v>
-      </c>
-      <c r="M101">
-        <v>1945.4795316</v>
-      </c>
-      <c r="N101">
-        <v>-113.5795315999999</v>
-      </c>
-      <c r="O101">
-        <v>-34.07385947999996</v>
-      </c>
-      <c r="P101">
-        <v>-79.50567211999993</v>
-      </c>
-      <c r="Q101">
-        <v>320.4943278800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.294482628260285</v>
-      </c>
-      <c r="T101">
-        <v>47.27229064057877</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.2824856242758941</v>
-      </c>
-      <c r="W101">
-        <v>0.08509720496087897</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9416187475863137</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
